--- a/data/sports/lol/gated.xlsx
+++ b/data/sports/lol/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ205" headerRowCount="1">
-  <autoFilter ref="A1:DQ205"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ210" headerRowCount="1">
+  <autoFilter ref="A1:DQ210"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$205)</f>
+        <f>COUNTA('Picks'!$A$2:$A$210)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$205,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$210,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$205,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$210,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"win")+COUNTIFS('Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")+COUNTIFS('Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$205,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$210,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$205,"&gt;0",'Picks'!$V$2:$V$205,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$205,"&gt;0",'Picks'!$V$2:$V$205,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$205,"&gt;0",'Picks'!$V$2:$V$205,"win")/(COUNTIFS('Picks'!$BX$2:$BX$205,"&gt;0",'Picks'!$V$2:$V$205,"win")+COUNTIFS('Picks'!$BX$2:$BX$205,"&gt;0",'Picks'!$V$2:$V$205,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")/(COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")+COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$205)/SUM('Picks'!$BX$2:$BX$205),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$210)/SUM('Picks'!$BX$2:$BX$210),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$205)</f>
+        <f>SUM('Picks'!$BY$2:$BY$210)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$205,"&lt;&gt;",'Picks'!$AB$2:$AB$205),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$210,"&lt;&gt;",'Picks'!$AB$2:$AB$210),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$205,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$205,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$210,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$210,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$205,'Picks'!$AM$2:$AM$205,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$210,'Picks'!$AM$2:$AM$210,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A14,'Picks'!$U$2:$U$205,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A14,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A14,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$205,'Picks'!$H$2:$H$205,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$205,'Picks'!$H$2:$H$205,$A14,'Picks'!$U$2:$U$205,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A15,'Picks'!$U$2:$U$205,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A15,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A15,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$205,'Picks'!$H$2:$H$205,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$205,'Picks'!$H$2:$H$205,$A15,'Picks'!$U$2:$U$205,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A16,'Picks'!$U$2:$U$205,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A16,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$205,$A16,'Picks'!$U$2:$U$205,"settled",'Picks'!$V$2:$V$205,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$205,'Picks'!$H$2:$H$205,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$205,'Picks'!$H$2:$H$205,$A16,'Picks'!$U$2:$U$205,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ205"/>
+  <dimension ref="A1:DQ210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -66805,18 +66805,38 @@
       </c>
       <c r="U205" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V205" s="24" t="n"/>
-      <c r="W205" s="26" t="n"/>
-      <c r="X205" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V205" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W205" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X205" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y205" s="25" t="n"/>
-      <c r="Z205" s="26" t="n"/>
-      <c r="AA205" s="28" t="n"/>
-      <c r="AB205" s="28" t="n"/>
-      <c r="AC205" s="30" t="n"/>
-      <c r="AD205" s="24" t="n"/>
+      <c r="Z205" s="26" t="n">
+        <v>-113</v>
+      </c>
+      <c r="AA205" s="28" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AB205" s="28" t="n">
+        <v>-0.009171</v>
+      </c>
+      <c r="AC205" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD205" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:04:31.026816Z</t>
+        </is>
+      </c>
       <c r="AE205" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-jdg-lgd-2026-10-06).</t>
@@ -66829,7 +66849,7 @@
       </c>
       <c r="AG205" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH205" s="24" t="n"/>
@@ -66959,8 +66979,12 @@
       <c r="BN205" s="28" t="n"/>
       <c r="BO205" s="28" t="n"/>
       <c r="BP205" s="25" t="n"/>
-      <c r="BQ205" s="27" t="n"/>
-      <c r="BR205" s="28" t="n"/>
+      <c r="BQ205" s="27" t="n">
+        <v>1.884956</v>
+      </c>
+      <c r="BR205" s="28" t="n">
+        <v>0.53</v>
+      </c>
       <c r="BS205" s="28" t="n"/>
       <c r="BT205" s="28" t="n"/>
       <c r="BU205" s="25" t="n"/>
@@ -67021,6 +67045,1491 @@
         </is>
       </c>
     </row>
+    <row r="206" ht="36" customHeight="1">
+      <c r="A206" s="24" t="inlineStr">
+        <is>
+          <t>4496e14ac5a64379</t>
+        </is>
+      </c>
+      <c r="B206" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.558378Z</t>
+        </is>
+      </c>
+      <c r="C206" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D206" s="24" t="inlineStr">
+        <is>
+          <t>143499</t>
+        </is>
+      </c>
+      <c r="E206" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F206" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="G206" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="H206" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I206" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J206" s="25" t="n"/>
+      <c r="K206" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L206" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M206" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N206" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O206" s="28" t="n">
+        <v>0.596948</v>
+      </c>
+      <c r="P206" s="28" t="n"/>
+      <c r="Q206" s="28" t="n">
+        <v>0.187112</v>
+      </c>
+      <c r="R206" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S206" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T206" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U206" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V206" s="24" t="n"/>
+      <c r="W206" s="26" t="n"/>
+      <c r="X206" s="26" t="n"/>
+      <c r="Y206" s="25" t="n"/>
+      <c r="Z206" s="26" t="n"/>
+      <c r="AA206" s="28" t="n"/>
+      <c r="AB206" s="28" t="n"/>
+      <c r="AC206" s="30" t="n"/>
+      <c r="AD206" s="24" t="n"/>
+      <c r="AE206" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-gam-sr-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF206" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG206" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH206" s="24" t="n"/>
+      <c r="AI206" s="31" t="n"/>
+      <c r="AJ206" s="31" t="n"/>
+      <c r="AK206" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL206" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM206" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN206" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO206" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP206" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AQ206" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AR206" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AS206" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AT206" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AU206" s="24" t="inlineStr">
+        <is>
+          <t>GAM Esports</t>
+        </is>
+      </c>
+      <c r="AV206" s="24" t="n"/>
+      <c r="AW206" s="24" t="n"/>
+      <c r="AX206" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY206" s="24" t="n"/>
+      <c r="AZ206" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA206" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BB206" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC206" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD206" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BE206" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF206" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG206" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH206" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:35.846879Z</t>
+        </is>
+      </c>
+      <c r="BI206" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ206" s="25" t="n"/>
+      <c r="BK206" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL206" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM206" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN206" s="28" t="n"/>
+      <c r="BO206" s="28" t="n"/>
+      <c r="BP206" s="25" t="n"/>
+      <c r="BQ206" s="27" t="n"/>
+      <c r="BR206" s="28" t="n"/>
+      <c r="BS206" s="28" t="n"/>
+      <c r="BT206" s="28" t="n"/>
+      <c r="BU206" s="25" t="n"/>
+      <c r="BV206" s="29" t="n"/>
+      <c r="BW206" s="24" t="n"/>
+      <c r="BX206" s="30" t="n"/>
+      <c r="BY206" s="27" t="n"/>
+      <c r="BZ206" s="24" t="n"/>
+      <c r="CA206" s="31" t="n"/>
+      <c r="CB206" s="24" t="n"/>
+      <c r="CC206" s="24" t="n"/>
+      <c r="CD206" s="24" t="n"/>
+      <c r="CE206" s="24" t="n"/>
+      <c r="CF206" s="24" t="n"/>
+      <c r="CG206" s="24" t="n"/>
+      <c r="CH206" s="24" t="n"/>
+      <c r="CI206" s="24" t="n"/>
+      <c r="CJ206" s="24" t="n"/>
+      <c r="CK206" s="24" t="n"/>
+      <c r="CL206" s="24" t="n"/>
+      <c r="CM206" s="24" t="n"/>
+      <c r="CN206" s="24" t="n"/>
+      <c r="CO206" s="24" t="n"/>
+      <c r="CP206" s="24" t="n"/>
+      <c r="CQ206" s="24" t="n"/>
+      <c r="CR206" s="24" t="n"/>
+      <c r="CS206" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT206" s="24" t="n"/>
+      <c r="CU206" s="24" t="n"/>
+      <c r="CV206" s="24" t="n"/>
+      <c r="CW206" s="24" t="n"/>
+      <c r="CX206" s="24" t="n"/>
+      <c r="CY206" s="24" t="n"/>
+      <c r="CZ206" s="24" t="n"/>
+      <c r="DA206" s="24" t="n"/>
+      <c r="DB206" s="24" t="n"/>
+      <c r="DC206" s="24" t="n"/>
+      <c r="DD206" s="24" t="n"/>
+      <c r="DE206" s="24" t="n"/>
+      <c r="DF206" s="24" t="n"/>
+      <c r="DG206" s="24" t="n"/>
+      <c r="DH206" s="24" t="n"/>
+      <c r="DI206" s="24" t="n"/>
+      <c r="DJ206" s="24" t="n"/>
+      <c r="DK206" s="24" t="n"/>
+      <c r="DL206" s="24" t="n"/>
+      <c r="DM206" s="24" t="n"/>
+      <c r="DN206" s="24" t="n"/>
+      <c r="DO206" s="24" t="n"/>
+      <c r="DP206" s="24" t="n"/>
+      <c r="DQ206" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Shopify Rebellion", "event_id": "143499", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1453.670775, "away_history_count": 72, "home_elo": 1542.604048, "home_history_count": 115}, "historical_source_observation_times_verified": false, "home_team": "GAM Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17572": 115, "bo3:3:18358": 72}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17572": "2026-10-05T07:00:00Z", "bo3:3:18358": "2026-10-05T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:17572": 1542.604048, "bo3:3:18358": 1453.670775}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:17572", "bo3:3:18358"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.403052, "home": 0.596948}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a1cc02a770badebe37add352725c9286332a0aff1ddcd5d0d4407cf8029c6a30", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="36" customHeight="1">
+      <c r="A207" s="24" t="inlineStr">
+        <is>
+          <t>4d2013ceb0c849b8</t>
+        </is>
+      </c>
+      <c r="B207" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.558378Z</t>
+        </is>
+      </c>
+      <c r="C207" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T11:00:00Z</t>
+        </is>
+      </c>
+      <c r="D207" s="24" t="inlineStr">
+        <is>
+          <t>143500</t>
+        </is>
+      </c>
+      <c r="E207" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F207" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="G207" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="H207" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I207" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J207" s="25" t="n"/>
+      <c r="K207" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L207" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M207" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N207" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O207" s="28" t="n">
+        <v>0.555596</v>
+      </c>
+      <c r="P207" s="28" t="n"/>
+      <c r="Q207" s="28" t="n">
+        <v>-0.084692</v>
+      </c>
+      <c r="R207" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S207" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T207" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U207" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V207" s="24" t="n"/>
+      <c r="W207" s="26" t="n"/>
+      <c r="X207" s="26" t="n"/>
+      <c r="Y207" s="25" t="n"/>
+      <c r="Z207" s="26" t="n"/>
+      <c r="AA207" s="28" t="n"/>
+      <c r="AB207" s="28" t="n"/>
+      <c r="AC207" s="30" t="n"/>
+      <c r="AD207" s="24" t="n"/>
+      <c r="AE207" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-fly-sr-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF207" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG207" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH207" s="24" t="n"/>
+      <c r="AI207" s="31" t="n"/>
+      <c r="AJ207" s="31" t="n"/>
+      <c r="AK207" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL207" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM207" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN207" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO207" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP207" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AQ207" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AR207" s="24" t="inlineStr">
+        <is>
+          <t>Shopify Rebellion</t>
+        </is>
+      </c>
+      <c r="AS207" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AT207" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AU207" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AV207" s="24" t="n"/>
+      <c r="AW207" s="24" t="n"/>
+      <c r="AX207" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY207" s="24" t="n"/>
+      <c r="AZ207" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA207" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BB207" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC207" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD207" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BE207" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF207" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG207" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH207" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:46.022169Z</t>
+        </is>
+      </c>
+      <c r="BI207" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ207" s="25" t="n"/>
+      <c r="BK207" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL207" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM207" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN207" s="28" t="n"/>
+      <c r="BO207" s="28" t="n"/>
+      <c r="BP207" s="25" t="n"/>
+      <c r="BQ207" s="27" t="n"/>
+      <c r="BR207" s="28" t="n"/>
+      <c r="BS207" s="28" t="n"/>
+      <c r="BT207" s="28" t="n"/>
+      <c r="BU207" s="25" t="n"/>
+      <c r="BV207" s="29" t="n"/>
+      <c r="BW207" s="24" t="n"/>
+      <c r="BX207" s="30" t="n"/>
+      <c r="BY207" s="27" t="n"/>
+      <c r="BZ207" s="24" t="n"/>
+      <c r="CA207" s="31" t="n"/>
+      <c r="CB207" s="24" t="n"/>
+      <c r="CC207" s="24" t="n"/>
+      <c r="CD207" s="24" t="n"/>
+      <c r="CE207" s="24" t="n"/>
+      <c r="CF207" s="24" t="n"/>
+      <c r="CG207" s="24" t="n"/>
+      <c r="CH207" s="24" t="n"/>
+      <c r="CI207" s="24" t="n"/>
+      <c r="CJ207" s="24" t="n"/>
+      <c r="CK207" s="24" t="n"/>
+      <c r="CL207" s="24" t="n"/>
+      <c r="CM207" s="24" t="n"/>
+      <c r="CN207" s="24" t="n"/>
+      <c r="CO207" s="24" t="n"/>
+      <c r="CP207" s="24" t="n"/>
+      <c r="CQ207" s="24" t="n"/>
+      <c r="CR207" s="24" t="n"/>
+      <c r="CS207" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT207" s="24" t="n"/>
+      <c r="CU207" s="24" t="n"/>
+      <c r="CV207" s="24" t="n"/>
+      <c r="CW207" s="24" t="n"/>
+      <c r="CX207" s="24" t="n"/>
+      <c r="CY207" s="24" t="n"/>
+      <c r="CZ207" s="24" t="n"/>
+      <c r="DA207" s="24" t="n"/>
+      <c r="DB207" s="24" t="n"/>
+      <c r="DC207" s="24" t="n"/>
+      <c r="DD207" s="24" t="n"/>
+      <c r="DE207" s="24" t="n"/>
+      <c r="DF207" s="24" t="n"/>
+      <c r="DG207" s="24" t="n"/>
+      <c r="DH207" s="24" t="n"/>
+      <c r="DI207" s="24" t="n"/>
+      <c r="DJ207" s="24" t="n"/>
+      <c r="DK207" s="24" t="n"/>
+      <c r="DL207" s="24" t="n"/>
+      <c r="DM207" s="24" t="n"/>
+      <c r="DN207" s="24" t="n"/>
+      <c r="DO207" s="24" t="n"/>
+      <c r="DP207" s="24" t="n"/>
+      <c r="DQ207" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Shopify Rebellion", "event_id": "143500", "event_start_utc": "2026-10-07T11:00:00Z", "features": {"away_elo": 1453.670775, "away_history_count": 72, "home_elo": 1497.784669, "home_history_count": 114}, "historical_source_observation_times_verified": false, "home_team": "FlyQuest", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18027": 114, "bo3:3:18358": 72}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18027": "2026-10-05T09:00:00Z", "bo3:3:18358": "2026-10-05T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:18027": 1497.784669, "bo3:3:18358": 1453.670775}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:18027", "bo3:3:18358"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.444404, "home": 0.555596}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "10f620eeff6fa8084afe07d81727848b0547c44702a3fac8764fbd1f5ee46fd4", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="36" customHeight="1">
+      <c r="A208" s="24" t="inlineStr">
+        <is>
+          <t>0d7b90d78f6b4561</t>
+        </is>
+      </c>
+      <c r="B208" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.558378Z</t>
+        </is>
+      </c>
+      <c r="C208" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D208" s="24" t="inlineStr">
+        <is>
+          <t>142769</t>
+        </is>
+      </c>
+      <c r="E208" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F208" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="G208" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="H208" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I208" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J208" s="25" t="n"/>
+      <c r="K208" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L208" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="M208" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="N208" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="O208" s="28" t="n">
+        <v>0.546158</v>
+      </c>
+      <c r="P208" s="28" t="n"/>
+      <c r="Q208" s="28" t="n">
+        <v>0.16593</v>
+      </c>
+      <c r="R208" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S208" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T208" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U208" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V208" s="24" t="n"/>
+      <c r="W208" s="26" t="n"/>
+      <c r="X208" s="26" t="n"/>
+      <c r="Y208" s="25" t="n"/>
+      <c r="Z208" s="26" t="n"/>
+      <c r="AA208" s="28" t="n"/>
+      <c r="AB208" s="28" t="n"/>
+      <c r="AC208" s="30" t="n"/>
+      <c r="AD208" s="24" t="n"/>
+      <c r="AE208" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-khk-use-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF208" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG208" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH208" s="24" t="n"/>
+      <c r="AI208" s="31" t="n"/>
+      <c r="AJ208" s="31" t="n"/>
+      <c r="AK208" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL208" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM208" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN208" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO208" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP208" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AQ208" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AR208" s="24" t="inlineStr">
+        <is>
+          <t>Unicorns Of Love Sexy Edition</t>
+        </is>
+      </c>
+      <c r="AS208" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AT208" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AU208" s="24" t="inlineStr">
+        <is>
+          <t>Kaufland Hangry Knights</t>
+        </is>
+      </c>
+      <c r="AV208" s="24" t="n"/>
+      <c r="AW208" s="24" t="n"/>
+      <c r="AX208" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY208" s="24" t="n"/>
+      <c r="AZ208" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA208" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BB208" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC208" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD208" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BE208" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF208" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG208" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH208" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:46.115100Z</t>
+        </is>
+      </c>
+      <c r="BI208" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ208" s="25" t="n"/>
+      <c r="BK208" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="BL208" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BM208" s="28" t="n">
+        <v>0.380228</v>
+      </c>
+      <c r="BN208" s="28" t="n"/>
+      <c r="BO208" s="28" t="n"/>
+      <c r="BP208" s="25" t="n"/>
+      <c r="BQ208" s="27" t="n"/>
+      <c r="BR208" s="28" t="n"/>
+      <c r="BS208" s="28" t="n"/>
+      <c r="BT208" s="28" t="n"/>
+      <c r="BU208" s="25" t="n"/>
+      <c r="BV208" s="29" t="n"/>
+      <c r="BW208" s="24" t="n"/>
+      <c r="BX208" s="30" t="n"/>
+      <c r="BY208" s="27" t="n"/>
+      <c r="BZ208" s="24" t="n"/>
+      <c r="CA208" s="31" t="n"/>
+      <c r="CB208" s="24" t="n"/>
+      <c r="CC208" s="24" t="n"/>
+      <c r="CD208" s="24" t="n"/>
+      <c r="CE208" s="24" t="n"/>
+      <c r="CF208" s="24" t="n"/>
+      <c r="CG208" s="24" t="n"/>
+      <c r="CH208" s="24" t="n"/>
+      <c r="CI208" s="24" t="n"/>
+      <c r="CJ208" s="24" t="n"/>
+      <c r="CK208" s="24" t="n"/>
+      <c r="CL208" s="24" t="n"/>
+      <c r="CM208" s="24" t="n"/>
+      <c r="CN208" s="24" t="n"/>
+      <c r="CO208" s="24" t="n"/>
+      <c r="CP208" s="24" t="n"/>
+      <c r="CQ208" s="24" t="n"/>
+      <c r="CR208" s="24" t="n"/>
+      <c r="CS208" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT208" s="24" t="n"/>
+      <c r="CU208" s="24" t="n"/>
+      <c r="CV208" s="24" t="n"/>
+      <c r="CW208" s="24" t="n"/>
+      <c r="CX208" s="24" t="n"/>
+      <c r="CY208" s="24" t="n"/>
+      <c r="CZ208" s="24" t="n"/>
+      <c r="DA208" s="24" t="n"/>
+      <c r="DB208" s="24" t="n"/>
+      <c r="DC208" s="24" t="n"/>
+      <c r="DD208" s="24" t="n"/>
+      <c r="DE208" s="24" t="n"/>
+      <c r="DF208" s="24" t="n"/>
+      <c r="DG208" s="24" t="n"/>
+      <c r="DH208" s="24" t="n"/>
+      <c r="DI208" s="24" t="n"/>
+      <c r="DJ208" s="24" t="n"/>
+      <c r="DK208" s="24" t="n"/>
+      <c r="DL208" s="24" t="n"/>
+      <c r="DM208" s="24" t="n"/>
+      <c r="DN208" s="24" t="n"/>
+      <c r="DO208" s="24" t="n"/>
+      <c r="DP208" s="24" t="n"/>
+      <c r="DQ208" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Unicorns Of Love Sexy Edition", "event_id": "142769", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1786.64817, "away_history_count": 146, "home_elo": 1722.623228, "home_history_count": 74}, "historical_source_observation_times_verified": false, "home_team": "Kaufland Hangry Knights", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16963": 74, "bo3:3:17414": 146}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16963": "2026-09-30T14:50:00Z", "bo3:3:17414": "2026-10-01T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16963": 1722.623228, "bo3:3:17414": 1786.64817}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16963", "bo3:3:17414"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.546158, "home": 0.453842}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1641aca9075bfcd5e1e4c42cacdf9686719bac31bcb8ab37f430186782e5510a", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="36" customHeight="1">
+      <c r="A209" s="24" t="inlineStr">
+        <is>
+          <t>ea80743efb1042c9</t>
+        </is>
+      </c>
+      <c r="B209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.558378Z</t>
+        </is>
+      </c>
+      <c r="C209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:00:00Z</t>
+        </is>
+      </c>
+      <c r="D209" s="24" t="inlineStr">
+        <is>
+          <t>142771</t>
+        </is>
+      </c>
+      <c r="E209" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F209" s="24" t="inlineStr">
+        <is>
+          <t>G2 NORD</t>
+        </is>
+      </c>
+      <c r="G209" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics Academy</t>
+        </is>
+      </c>
+      <c r="H209" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I209" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J209" s="25" t="n"/>
+      <c r="K209" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L209" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="M209" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="N209" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O209" s="28" t="n">
+        <v>0.507711</v>
+      </c>
+      <c r="P209" s="28" t="n"/>
+      <c r="Q209" s="28" t="n">
+        <v>-0.092289</v>
+      </c>
+      <c r="R209" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S209" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T209" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U209" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V209" s="24" t="n"/>
+      <c r="W209" s="26" t="n"/>
+      <c r="X209" s="26" t="n"/>
+      <c r="Y209" s="25" t="n"/>
+      <c r="Z209" s="26" t="n"/>
+      <c r="AA209" s="28" t="n"/>
+      <c r="AB209" s="28" t="n"/>
+      <c r="AC209" s="30" t="n"/>
+      <c r="AD209" s="24" t="n"/>
+      <c r="AE209" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-hrts-g2n-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF209" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG209" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH209" s="24" t="n"/>
+      <c r="AI209" s="31" t="n"/>
+      <c r="AJ209" s="31" t="n"/>
+      <c r="AK209" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL209" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM209" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN209" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO209" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP209" s="24" t="inlineStr">
+        <is>
+          <t>G2 NORD</t>
+        </is>
+      </c>
+      <c r="AQ209" s="24" t="inlineStr">
+        <is>
+          <t>G2 NORD</t>
+        </is>
+      </c>
+      <c r="AR209" s="24" t="inlineStr">
+        <is>
+          <t>G2 NORD</t>
+        </is>
+      </c>
+      <c r="AS209" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics Academy</t>
+        </is>
+      </c>
+      <c r="AT209" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics Academy</t>
+        </is>
+      </c>
+      <c r="AU209" s="24" t="inlineStr">
+        <is>
+          <t>Team Heretics Academy</t>
+        </is>
+      </c>
+      <c r="AV209" s="24" t="n"/>
+      <c r="AW209" s="24" t="n"/>
+      <c r="AX209" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY209" s="24" t="n"/>
+      <c r="AZ209" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA209" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BB209" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC209" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD209" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BE209" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF209" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG209" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:56.333090Z</t>
+        </is>
+      </c>
+      <c r="BI209" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ209" s="25" t="n"/>
+      <c r="BK209" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="BL209" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BM209" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="BN209" s="28" t="n"/>
+      <c r="BO209" s="28" t="n"/>
+      <c r="BP209" s="25" t="n"/>
+      <c r="BQ209" s="27" t="n"/>
+      <c r="BR209" s="28" t="n"/>
+      <c r="BS209" s="28" t="n"/>
+      <c r="BT209" s="28" t="n"/>
+      <c r="BU209" s="25" t="n"/>
+      <c r="BV209" s="29" t="n"/>
+      <c r="BW209" s="24" t="n"/>
+      <c r="BX209" s="30" t="n"/>
+      <c r="BY209" s="27" t="n"/>
+      <c r="BZ209" s="24" t="n"/>
+      <c r="CA209" s="31" t="n"/>
+      <c r="CB209" s="24" t="n"/>
+      <c r="CC209" s="24" t="n"/>
+      <c r="CD209" s="24" t="n"/>
+      <c r="CE209" s="24" t="n"/>
+      <c r="CF209" s="24" t="n"/>
+      <c r="CG209" s="24" t="n"/>
+      <c r="CH209" s="24" t="n"/>
+      <c r="CI209" s="24" t="n"/>
+      <c r="CJ209" s="24" t="n"/>
+      <c r="CK209" s="24" t="n"/>
+      <c r="CL209" s="24" t="n"/>
+      <c r="CM209" s="24" t="n"/>
+      <c r="CN209" s="24" t="n"/>
+      <c r="CO209" s="24" t="n"/>
+      <c r="CP209" s="24" t="n"/>
+      <c r="CQ209" s="24" t="n"/>
+      <c r="CR209" s="24" t="n"/>
+      <c r="CS209" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT209" s="24" t="n"/>
+      <c r="CU209" s="24" t="n"/>
+      <c r="CV209" s="24" t="n"/>
+      <c r="CW209" s="24" t="n"/>
+      <c r="CX209" s="24" t="n"/>
+      <c r="CY209" s="24" t="n"/>
+      <c r="CZ209" s="24" t="n"/>
+      <c r="DA209" s="24" t="n"/>
+      <c r="DB209" s="24" t="n"/>
+      <c r="DC209" s="24" t="n"/>
+      <c r="DD209" s="24" t="n"/>
+      <c r="DE209" s="24" t="n"/>
+      <c r="DF209" s="24" t="n"/>
+      <c r="DG209" s="24" t="n"/>
+      <c r="DH209" s="24" t="n"/>
+      <c r="DI209" s="24" t="n"/>
+      <c r="DJ209" s="24" t="n"/>
+      <c r="DK209" s="24" t="n"/>
+      <c r="DL209" s="24" t="n"/>
+      <c r="DM209" s="24" t="n"/>
+      <c r="DN209" s="24" t="n"/>
+      <c r="DO209" s="24" t="n"/>
+      <c r="DP209" s="24" t="n"/>
+      <c r="DQ209" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "G2 NORD", "event_id": "142771", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1916.811779, "away_history_count": 61, "home_elo": 1892.657889, "home_history_count": 157}, "historical_source_observation_times_verified": false, "home_team": "Team Heretics Academy", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16945": 157, "bo3:3:22411": 61}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16945": "2026-09-30T17:30:00Z", "bo3:3:22411": "2026-09-30T16:35:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16945": 1892.657889, "bo3:3:22411": 1916.811779}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16945", "bo3:3:22411"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.507711, "home": 0.492289}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "745fa96b0a908fa8a54d7683111edc4af13ed9b8ca0517c655acbae05e65795c", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="36" customHeight="1">
+      <c r="A210" s="24" t="inlineStr">
+        <is>
+          <t>a8edc2ac380f4cf6</t>
+        </is>
+      </c>
+      <c r="B210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.558378Z</t>
+        </is>
+      </c>
+      <c r="C210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T21:00:00Z</t>
+        </is>
+      </c>
+      <c r="D210" s="24" t="inlineStr">
+        <is>
+          <t>144660</t>
+        </is>
+      </c>
+      <c r="E210" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F210" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="G210" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="H210" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I210" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J210" s="25" t="n"/>
+      <c r="K210" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L210" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="M210" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="N210" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="O210" s="28" t="n">
+        <v>0.718247</v>
+      </c>
+      <c r="P210" s="28" t="n"/>
+      <c r="Q210" s="28" t="n">
+        <v>0.397734</v>
+      </c>
+      <c r="R210" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S210" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T210" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U210" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V210" s="24" t="n"/>
+      <c r="W210" s="26" t="n"/>
+      <c r="X210" s="26" t="n"/>
+      <c r="Y210" s="25" t="n"/>
+      <c r="Z210" s="26" t="n"/>
+      <c r="AA210" s="28" t="n"/>
+      <c r="AB210" s="28" t="n"/>
+      <c r="AC210" s="30" t="n"/>
+      <c r="AD210" s="24" t="n"/>
+      <c r="AE210" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-lol-dsg-mvu-2026-10-07).</t>
+        </is>
+      </c>
+      <c r="AF210" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG210" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH210" s="24" t="n"/>
+      <c r="AI210" s="31" t="n"/>
+      <c r="AJ210" s="31" t="n"/>
+      <c r="AK210" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL210" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM210" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN210" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO210" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP210" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AQ210" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AR210" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AS210" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AT210" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AU210" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AV210" s="24" t="n"/>
+      <c r="AW210" s="24" t="n"/>
+      <c r="AX210" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY210" s="24" t="n"/>
+      <c r="AZ210" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA210" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BB210" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC210" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD210" s="24" t="inlineStr">
+        <is>
+          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+        </is>
+      </c>
+      <c r="BE210" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF210" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG210" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:26:06.541945Z</t>
+        </is>
+      </c>
+      <c r="BI210" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ210" s="25" t="n"/>
+      <c r="BK210" s="26" t="n">
+        <v>212</v>
+      </c>
+      <c r="BL210" s="27" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BM210" s="28" t="n">
+        <v>0.320513</v>
+      </c>
+      <c r="BN210" s="28" t="n"/>
+      <c r="BO210" s="28" t="n"/>
+      <c r="BP210" s="25" t="n"/>
+      <c r="BQ210" s="27" t="n"/>
+      <c r="BR210" s="28" t="n"/>
+      <c r="BS210" s="28" t="n"/>
+      <c r="BT210" s="28" t="n"/>
+      <c r="BU210" s="25" t="n"/>
+      <c r="BV210" s="29" t="n"/>
+      <c r="BW210" s="24" t="n"/>
+      <c r="BX210" s="30" t="n"/>
+      <c r="BY210" s="27" t="n"/>
+      <c r="BZ210" s="24" t="n"/>
+      <c r="CA210" s="31" t="n"/>
+      <c r="CB210" s="24" t="n"/>
+      <c r="CC210" s="24" t="n"/>
+      <c r="CD210" s="24" t="n"/>
+      <c r="CE210" s="24" t="n"/>
+      <c r="CF210" s="24" t="n"/>
+      <c r="CG210" s="24" t="n"/>
+      <c r="CH210" s="24" t="n"/>
+      <c r="CI210" s="24" t="n"/>
+      <c r="CJ210" s="24" t="n"/>
+      <c r="CK210" s="24" t="n"/>
+      <c r="CL210" s="24" t="n"/>
+      <c r="CM210" s="24" t="n"/>
+      <c r="CN210" s="24" t="n"/>
+      <c r="CO210" s="24" t="n"/>
+      <c r="CP210" s="24" t="n"/>
+      <c r="CQ210" s="24" t="n"/>
+      <c r="CR210" s="24" t="n"/>
+      <c r="CS210" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT210" s="24" t="n"/>
+      <c r="CU210" s="24" t="n"/>
+      <c r="CV210" s="24" t="n"/>
+      <c r="CW210" s="24" t="n"/>
+      <c r="CX210" s="24" t="n"/>
+      <c r="CY210" s="24" t="n"/>
+      <c r="CZ210" s="24" t="n"/>
+      <c r="DA210" s="24" t="n"/>
+      <c r="DB210" s="24" t="n"/>
+      <c r="DC210" s="24" t="n"/>
+      <c r="DD210" s="24" t="n"/>
+      <c r="DE210" s="24" t="n"/>
+      <c r="DF210" s="24" t="n"/>
+      <c r="DG210" s="24" t="n"/>
+      <c r="DH210" s="24" t="n"/>
+      <c r="DI210" s="24" t="n"/>
+      <c r="DJ210" s="24" t="n"/>
+      <c r="DK210" s="24" t="n"/>
+      <c r="DL210" s="24" t="n"/>
+      <c r="DM210" s="24" t="n"/>
+      <c r="DN210" s="24" t="n"/>
+      <c r="DO210" s="24" t="n"/>
+      <c r="DP210" s="24" t="n"/>
+      <c r="DQ210" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Maryville University", "event_id": "144660", "event_start_utc": "2026-10-07T21:00:00Z", "features": {"away_elo": 1646.662988, "away_history_count": 38, "home_elo": 1354.432648, "home_history_count": 67}, "historical_source_observation_times_verified": false, "home_team": "Disguised", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16807": 67, "bo3:3:17077": 38}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16807": "2026-09-06T21:45:00Z", "bo3:3:17077": "2026-10-05T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16807": 1354.432648, "bo3:3:17077": 1646.662988}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16807", "bo3:3:17077"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.718247, "home": 0.281753}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "02872a08071111d998018facd70075414cb67dbd056b333d338af579a3162252", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/lol/gated.xlsx
+++ b/data/sports/lol/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ210" headerRowCount="1">
-  <autoFilter ref="A1:DQ210"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ215" headerRowCount="1">
+  <autoFilter ref="A1:DQ215"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$210)</f>
+        <f>COUNTA('Picks'!$A$2:$A$215)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$210,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$215,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$210,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")+COUNTIFS('Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$210,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$215,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")/(COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"win")+COUNTIFS('Picks'!$BX$2:$BX$210,"&gt;0",'Picks'!$V$2:$V$210,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")/(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$210)/SUM('Picks'!$BX$2:$BX$210),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$215)/SUM('Picks'!$BX$2:$BX$215),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$210)</f>
+        <f>SUM('Picks'!$BY$2:$BY$215)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$210,"&lt;&gt;",'Picks'!$AB$2:$AB$210),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$215,"&lt;&gt;",'Picks'!$AB$2:$AB$215),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$210,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$210,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$210,'Picks'!$AM$2:$AM$210,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$215,'Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A14,'Picks'!$U$2:$U$210,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A15,'Picks'!$U$2:$U$210,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled",'Picks'!$V$2:$V$210,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$210,'Picks'!$H$2:$H$210,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$210,'Picks'!$H$2:$H$210,$A16,'Picks'!$U$2:$U$210,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ210"/>
+  <dimension ref="A1:DQ215"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -67048,12 +67048,12 @@
     <row r="206" ht="36" customHeight="1">
       <c r="A206" s="24" t="inlineStr">
         <is>
-          <t>4496e14ac5a64379</t>
+          <t>2e00726b287f40f3</t>
         </is>
       </c>
       <c r="B206" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.558378Z</t>
+          <t>2026-10-07T05:30:02.936253Z</t>
         </is>
       </c>
       <c r="C206" s="24" t="inlineStr">
@@ -67098,26 +67098,26 @@
         </is>
       </c>
       <c r="L206" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="M206" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="N206" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="O206" s="28" t="n">
-        <v>0.596948</v>
+        <v>0.596761</v>
       </c>
       <c r="P206" s="28" t="n"/>
       <c r="Q206" s="28" t="n">
-        <v>0.187112</v>
+        <v>0.176593</v>
       </c>
       <c r="R206" s="26" t="n">
         <v>100</v>
       </c>
       <c r="S206" s="29" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="T206" s="24" t="inlineStr">
         <is>
@@ -67126,21 +67126,41 @@
       </c>
       <c r="U206" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V206" s="24" t="n"/>
-      <c r="W206" s="26" t="n"/>
-      <c r="X206" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V206" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W206" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X206" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y206" s="25" t="n"/>
-      <c r="Z206" s="26" t="n"/>
-      <c r="AA206" s="28" t="n"/>
-      <c r="AB206" s="28" t="n"/>
-      <c r="AC206" s="30" t="n"/>
-      <c r="AD206" s="24" t="n"/>
+      <c r="Z206" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="AA206" s="28" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AB206" s="28" t="n">
+        <v>-0.000168</v>
+      </c>
+      <c r="AC206" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD206" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T10:06:01.180935Z</t>
+        </is>
+      </c>
       <c r="AE206" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-gam-sr-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.4200 (market_slug=aec-lol-gam-sr-2026-10-07).</t>
         </is>
       </c>
       <c r="AF206" s="31" t="inlineStr">
@@ -67150,7 +67170,7 @@
       </c>
       <c r="AG206" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH206" s="24" t="n"/>
@@ -67224,7 +67244,7 @@
       </c>
       <c r="BA206" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>af470c57db1077f59bc43ec3332bc3a69fa8772386bf0a1281c4433bf8acc58d</t>
         </is>
       </c>
       <c r="BB206" s="24" t="inlineStr">
@@ -67239,7 +67259,7 @@
       </c>
       <c r="BD206" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>af470c57db1077f59bc43ec3332bc3a69fa8772386bf0a1281c4433bf8acc58d</t>
         </is>
       </c>
       <c r="BE206" s="24" t="inlineStr">
@@ -67259,7 +67279,7 @@
       </c>
       <c r="BH206" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:35.846879Z</t>
+          <t>2026-10-07T05:29:00.002152Z</t>
         </is>
       </c>
       <c r="BI206" s="24" t="inlineStr">
@@ -67269,19 +67289,23 @@
       </c>
       <c r="BJ206" s="25" t="n"/>
       <c r="BK206" s="26" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="BL206" s="27" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="BM206" s="28" t="n">
-        <v>0.409836</v>
+        <v>0.420168</v>
       </c>
       <c r="BN206" s="28" t="n"/>
       <c r="BO206" s="28" t="n"/>
       <c r="BP206" s="25" t="n"/>
-      <c r="BQ206" s="27" t="n"/>
-      <c r="BR206" s="28" t="n"/>
+      <c r="BQ206" s="27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BR206" s="28" t="n">
+        <v>0.42</v>
+      </c>
       <c r="BS206" s="28" t="n"/>
       <c r="BT206" s="28" t="n"/>
       <c r="BU206" s="25" t="n"/>
@@ -67338,29 +67362,29 @@
       <c r="DP206" s="24" t="n"/>
       <c r="DQ206" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Shopify Rebellion", "event_id": "143499", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1453.670775, "away_history_count": 72, "home_elo": 1542.604048, "home_history_count": 115}, "historical_source_observation_times_verified": false, "home_team": "GAM Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17572": 115, "bo3:3:18358": 72}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17572": "2026-10-05T07:00:00Z", "bo3:3:18358": "2026-10-05T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:17572": 1542.604048, "bo3:3:18358": 1453.670775}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:17572", "bo3:3:18358"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.403052, "home": 0.596948}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a1cc02a770badebe37add352725c9286332a0aff1ddcd5d0d4407cf8029c6a30", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "af470c57db1077f59bc43ec3332bc3a69fa8772386bf0a1281c4433bf8acc58d", "away_team": "Shopify Rebellion", "event_id": "143499", "event_start_utc": "2026-10-07T09:00:00Z", "features": {"away_elo": 1453.640627, "away_history_count": 72, "home_elo": 1542.596001, "home_history_count": 115}, "historical_source_observation_times_verified": false, "home_team": "GAM Esports", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17572": 115, "bo3:3:18358": 72}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17572": "2026-10-05T07:00:00Z", "bo3:3:18358": "2026-10-05T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06650010106940477, "platt_slope": 0.786729387648304, "ratings": {"bo3:3:17572": 1542.596001, "bo3:3:18358": 1453.640627}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T05:28:49.652280+00:00", "team_ids": ["bo3:3:17572", "bo3:3:18358"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-07T05:28:49.652280+00:00", "probabilities": {"away": 0.403239, "home": 0.596761}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e0c62ff68b4faf4404b0dc3d6f0d9704049626f4ca21c81b1abe7a6255a6b05e", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
     <row r="207" ht="36" customHeight="1">
       <c r="A207" s="24" t="inlineStr">
         <is>
-          <t>4d2013ceb0c849b8</t>
+          <t>b1c5d7bad40f4159</t>
         </is>
       </c>
       <c r="B207" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.558378Z</t>
+          <t>2026-10-07T10:23:29.866453Z</t>
         </is>
       </c>
       <c r="C207" s="24" t="inlineStr">
         <is>
-          <t>2026-10-07T11:00:00Z</t>
+          <t>2026-10-07T16:00:00Z</t>
         </is>
       </c>
       <c r="D207" s="24" t="inlineStr">
         <is>
-          <t>143500</t>
+          <t>142769</t>
         </is>
       </c>
       <c r="E207" s="24" t="inlineStr">
@@ -67370,12 +67394,12 @@
       </c>
       <c r="F207" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>Unicorns Of Love Sexy Edition</t>
         </is>
       </c>
       <c r="G207" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="H207" s="24" t="inlineStr">
@@ -67385,7 +67409,7 @@
       </c>
       <c r="I207" s="24" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>away</t>
         </is>
       </c>
       <c r="J207" s="25" t="n"/>
@@ -67395,49 +67419,69 @@
         </is>
       </c>
       <c r="L207" s="26" t="n">
-        <v>-178</v>
+        <v>150</v>
       </c>
       <c r="M207" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.5</v>
       </c>
       <c r="N207" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.4</v>
       </c>
       <c r="O207" s="28" t="n">
-        <v>0.555596</v>
+        <v>0.545756</v>
       </c>
       <c r="P207" s="28" t="n"/>
       <c r="Q207" s="28" t="n">
-        <v>-0.084692</v>
+        <v>0.145756</v>
       </c>
       <c r="R207" s="26" t="n">
+        <v>93</v>
+      </c>
+      <c r="S207" s="29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="T207" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U207" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V207" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W207" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="S207" s="29" t="n">
+      <c r="X207" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="T207" s="24" t="inlineStr">
-        <is>
-          <t>lol-tiered-elo-v6</t>
-        </is>
-      </c>
-      <c r="U207" s="24" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V207" s="24" t="n"/>
-      <c r="W207" s="26" t="n"/>
-      <c r="X207" s="26" t="n"/>
       <c r="Y207" s="25" t="n"/>
-      <c r="Z207" s="26" t="n"/>
-      <c r="AA207" s="28" t="n"/>
-      <c r="AB207" s="28" t="n"/>
-      <c r="AC207" s="30" t="n"/>
-      <c r="AD207" s="24" t="n"/>
+      <c r="Z207" s="26" t="n">
+        <v>163</v>
+      </c>
+      <c r="AA207" s="28" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB207" s="28" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="AC207" s="30" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="AD207" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:04:57.586850Z</t>
+        </is>
+      </c>
       <c r="AE207" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6400 (market_slug=aec-lol-fly-sr-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.4000 (market_slug=aec-lol-khk-use-2026-10-07).</t>
         </is>
       </c>
       <c r="AF207" s="31" t="inlineStr">
@@ -67447,7 +67491,7 @@
       </c>
       <c r="AG207" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH207" s="24" t="n"/>
@@ -67455,7 +67499,7 @@
       <c r="AJ207" s="31" t="n"/>
       <c r="AK207" s="24" t="inlineStr">
         <is>
-          <t>paper_call</t>
+          <t>model_qualified</t>
         </is>
       </c>
       <c r="AL207" s="26" t="n">
@@ -67463,7 +67507,7 @@
       </c>
       <c r="AM207" s="24" t="inlineStr">
         <is>
-          <t>RESEARCH_OBSERVATION</t>
+          <t>QUALIFIED_SHADOW_CALL</t>
         </is>
       </c>
       <c r="AN207" s="24" t="inlineStr">
@@ -67473,37 +67517,37 @@
       </c>
       <c r="AO207" s="24" t="inlineStr">
         <is>
-          <t>PAPER_CALL_LOW_EDGE</t>
+          <t>QUALIFIED</t>
         </is>
       </c>
       <c r="AP207" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>Unicorns Of Love Sexy Edition</t>
         </is>
       </c>
       <c r="AQ207" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>Unicorns Of Love Sexy Edition</t>
         </is>
       </c>
       <c r="AR207" s="24" t="inlineStr">
         <is>
-          <t>Shopify Rebellion</t>
+          <t>Unicorns Of Love Sexy Edition</t>
         </is>
       </c>
       <c r="AS207" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AT207" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AU207" s="24" t="inlineStr">
         <is>
-          <t>FlyQuest</t>
+          <t>Kaufland Hangry Knights</t>
         </is>
       </c>
       <c r="AV207" s="24" t="n"/>
@@ -67521,7 +67565,7 @@
       </c>
       <c r="BA207" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3</t>
         </is>
       </c>
       <c r="BB207" s="24" t="inlineStr">
@@ -67536,7 +67580,7 @@
       </c>
       <c r="BD207" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3</t>
         </is>
       </c>
       <c r="BE207" s="24" t="inlineStr">
@@ -67556,7 +67600,7 @@
       </c>
       <c r="BH207" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:46.022169Z</t>
+          <t>2026-10-07T10:23:09.262846Z</t>
         </is>
       </c>
       <c r="BI207" s="24" t="inlineStr">
@@ -67566,19 +67610,23 @@
       </c>
       <c r="BJ207" s="25" t="n"/>
       <c r="BK207" s="26" t="n">
-        <v>-178</v>
+        <v>150</v>
       </c>
       <c r="BL207" s="27" t="n">
-        <v>1.561798</v>
+        <v>2.5</v>
       </c>
       <c r="BM207" s="28" t="n">
-        <v>0.640288</v>
+        <v>0.4</v>
       </c>
       <c r="BN207" s="28" t="n"/>
       <c r="BO207" s="28" t="n"/>
       <c r="BP207" s="25" t="n"/>
-      <c r="BQ207" s="27" t="n"/>
-      <c r="BR207" s="28" t="n"/>
+      <c r="BQ207" s="27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="BR207" s="28" t="n">
+        <v>0.38</v>
+      </c>
       <c r="BS207" s="28" t="n"/>
       <c r="BT207" s="28" t="n"/>
       <c r="BU207" s="25" t="n"/>
@@ -67607,7 +67655,7 @@
       <c r="CR207" s="24" t="n"/>
       <c r="CS207" s="24" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="CT207" s="24" t="n"/>
@@ -67635,19 +67683,19 @@
       <c r="DP207" s="24" t="n"/>
       <c r="DQ207" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Shopify Rebellion", "event_id": "143500", "event_start_utc": "2026-10-07T11:00:00Z", "features": {"away_elo": 1453.670775, "away_history_count": 72, "home_elo": 1497.784669, "home_history_count": 114}, "historical_source_observation_times_verified": false, "home_team": "FlyQuest", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18027": 114, "bo3:3:18358": 72}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18027": "2026-10-05T09:00:00Z", "bo3:3:18358": "2026-10-05T10:40:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:18027": 1497.784669, "bo3:3:18358": 1453.670775}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:18027", "bo3:3:18358"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.444404, "home": 0.555596}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "10f620eeff6fa8084afe07d81727848b0547c44702a3fac8764fbd1f5ee46fd4", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3", "away_team": "Unicorns Of Love Sexy Edition", "event_id": "142769", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1786.544458, "away_history_count": 146, "home_elo": 1722.438214, "home_history_count": 74}, "historical_source_observation_times_verified": false, "home_team": "Kaufland Hangry Knights", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16963": 74, "bo3:3:17414": 146}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16963": "2026-09-30T14:50:00Z", "bo3:3:17414": "2026-10-01T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06737474926872696, "platt_slope": 0.7868004676862648, "ratings": {"bo3:3:16963": 1722.438214, "bo3:3:17414": 1786.544458}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T10:23:09.212163+00:00", "team_ids": ["bo3:3:16963", "bo3:3:17414"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-07T10:23:09.212163+00:00", "probabilities": {"away": 0.545756, "home": 0.454244}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "7580d0f84fde89cc5ff0da5a99b520782310bf119faa2705d1f0a5c7661a3e2b", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
     <row r="208" ht="36" customHeight="1">
       <c r="A208" s="24" t="inlineStr">
         <is>
-          <t>0d7b90d78f6b4561</t>
+          <t>e914708ffd0f4d56</t>
         </is>
       </c>
       <c r="B208" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.558378Z</t>
+          <t>2026-10-07T10:23:29.866453Z</t>
         </is>
       </c>
       <c r="C208" s="24" t="inlineStr">
@@ -67657,7 +67705,7 @@
       </c>
       <c r="D208" s="24" t="inlineStr">
         <is>
-          <t>142769</t>
+          <t>142771</t>
         </is>
       </c>
       <c r="E208" s="24" t="inlineStr">
@@ -67667,12 +67715,12 @@
       </c>
       <c r="F208" s="24" t="inlineStr">
         <is>
-          <t>Unicorns Of Love Sexy Edition</t>
+          <t>G2 NORD</t>
         </is>
       </c>
       <c r="G208" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>Team Heretics Academy</t>
         </is>
       </c>
       <c r="H208" s="24" t="inlineStr">
@@ -67692,26 +67740,26 @@
         </is>
       </c>
       <c r="L208" s="26" t="n">
-        <v>163</v>
+        <v>-233</v>
       </c>
       <c r="M208" s="27" t="n">
-        <v>2.63</v>
+        <v>1.429185</v>
       </c>
       <c r="N208" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.6997</v>
       </c>
       <c r="O208" s="28" t="n">
-        <v>0.546158</v>
+        <v>0.507418</v>
       </c>
       <c r="P208" s="28" t="n"/>
       <c r="Q208" s="28" t="n">
-        <v>0.16593</v>
+        <v>-0.192282</v>
       </c>
       <c r="R208" s="26" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="S208" s="29" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="T208" s="24" t="inlineStr">
         <is>
@@ -67720,21 +67768,41 @@
       </c>
       <c r="U208" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V208" s="24" t="n"/>
-      <c r="W208" s="26" t="n"/>
-      <c r="X208" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V208" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W208" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X208" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y208" s="25" t="n"/>
-      <c r="Z208" s="26" t="n"/>
-      <c r="AA208" s="28" t="n"/>
-      <c r="AB208" s="28" t="n"/>
-      <c r="AC208" s="30" t="n"/>
-      <c r="AD208" s="24" t="n"/>
+      <c r="Z208" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="AA208" s="28" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AB208" s="28" t="n">
+        <v>-0.0897</v>
+      </c>
+      <c r="AC208" s="30" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="AD208" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T22:04:59.281471Z</t>
+        </is>
+      </c>
       <c r="AE208" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3800 (market_slug=aec-lol-khk-use-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-hrts-g2n-2026-10-07).</t>
         </is>
       </c>
       <c r="AF208" s="31" t="inlineStr">
@@ -67752,7 +67820,7 @@
       <c r="AJ208" s="31" t="n"/>
       <c r="AK208" s="24" t="inlineStr">
         <is>
-          <t>model_qualified</t>
+          <t>paper_call</t>
         </is>
       </c>
       <c r="AL208" s="26" t="n">
@@ -67760,7 +67828,7 @@
       </c>
       <c r="AM208" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED_SHADOW_CALL</t>
+          <t>RESEARCH_OBSERVATION</t>
         </is>
       </c>
       <c r="AN208" s="24" t="inlineStr">
@@ -67770,37 +67838,37 @@
       </c>
       <c r="AO208" s="24" t="inlineStr">
         <is>
-          <t>QUALIFIED</t>
+          <t>PAPER_CALL_LOW_EDGE</t>
         </is>
       </c>
       <c r="AP208" s="24" t="inlineStr">
         <is>
-          <t>Unicorns Of Love Sexy Edition</t>
+          <t>G2 NORD</t>
         </is>
       </c>
       <c r="AQ208" s="24" t="inlineStr">
         <is>
-          <t>Unicorns Of Love Sexy Edition</t>
+          <t>G2 NORD</t>
         </is>
       </c>
       <c r="AR208" s="24" t="inlineStr">
         <is>
-          <t>Unicorns Of Love Sexy Edition</t>
+          <t>G2 NORD</t>
         </is>
       </c>
       <c r="AS208" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>Team Heretics Academy</t>
         </is>
       </c>
       <c r="AT208" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>Team Heretics Academy</t>
         </is>
       </c>
       <c r="AU208" s="24" t="inlineStr">
         <is>
-          <t>Kaufland Hangry Knights</t>
+          <t>Team Heretics Academy</t>
         </is>
       </c>
       <c r="AV208" s="24" t="n"/>
@@ -67818,7 +67886,7 @@
       </c>
       <c r="BA208" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3</t>
         </is>
       </c>
       <c r="BB208" s="24" t="inlineStr">
@@ -67833,7 +67901,7 @@
       </c>
       <c r="BD208" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3</t>
         </is>
       </c>
       <c r="BE208" s="24" t="inlineStr">
@@ -67853,7 +67921,7 @@
       </c>
       <c r="BH208" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:46.115100Z</t>
+          <t>2026-10-07T10:23:29.745491Z</t>
         </is>
       </c>
       <c r="BI208" s="24" t="inlineStr">
@@ -67863,19 +67931,23 @@
       </c>
       <c r="BJ208" s="25" t="n"/>
       <c r="BK208" s="26" t="n">
-        <v>163</v>
+        <v>-233</v>
       </c>
       <c r="BL208" s="27" t="n">
-        <v>2.63</v>
+        <v>1.429185</v>
       </c>
       <c r="BM208" s="28" t="n">
-        <v>0.380228</v>
+        <v>0.6997</v>
       </c>
       <c r="BN208" s="28" t="n"/>
       <c r="BO208" s="28" t="n"/>
       <c r="BP208" s="25" t="n"/>
-      <c r="BQ208" s="27" t="n"/>
-      <c r="BR208" s="28" t="n"/>
+      <c r="BQ208" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BR208" s="28" t="n">
+        <v>0.61</v>
+      </c>
       <c r="BS208" s="28" t="n"/>
       <c r="BT208" s="28" t="n"/>
       <c r="BU208" s="25" t="n"/>
@@ -67904,7 +67976,7 @@
       <c r="CR208" s="24" t="n"/>
       <c r="CS208" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT208" s="24" t="n"/>
@@ -67932,29 +68004,29 @@
       <c r="DP208" s="24" t="n"/>
       <c r="DQ208" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Unicorns Of Love Sexy Edition", "event_id": "142769", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1786.64817, "away_history_count": 146, "home_elo": 1722.623228, "home_history_count": 74}, "historical_source_observation_times_verified": false, "home_team": "Kaufland Hangry Knights", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16963": 74, "bo3:3:17414": 146}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16963": "2026-09-30T14:50:00Z", "bo3:3:17414": "2026-10-01T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16963": 1722.623228, "bo3:3:17414": 1786.64817}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16963", "bo3:3:17414"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.546158, "home": 0.453842}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "1641aca9075bfcd5e1e4c42cacdf9686719bac31bcb8ab37f430186782e5510a", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "2ca11595ae1334d11ecce05380a0a53ce290154b730cc6d01bd66ecde0433fc3", "away_team": "G2 NORD", "event_id": "142771", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1916.720158, "away_history_count": 61, "home_elo": 1892.558669, "home_history_count": 157}, "historical_source_observation_times_verified": false, "home_team": "Team Heretics Academy", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16945": 157, "bo3:3:22411": 61}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16945": "2026-09-30T17:30:00Z", "bo3:3:22411": "2026-09-30T16:35:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06737474926872696, "platt_slope": 0.7868004676862648, "ratings": {"bo3:3:16945": 1892.558669, "bo3:3:22411": 1916.720158}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-07T10:23:09.212163+00:00", "team_ids": ["bo3:3:16945", "bo3:3:22411"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-07T10:23:09.212163+00:00", "probabilities": {"away": 0.507418, "home": 0.492582}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "dec17fa454efab03100315fe8322274d5152e3a35fbe1f82621d0059cea7299c", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
     <row r="209" ht="36" customHeight="1">
       <c r="A209" s="24" t="inlineStr">
         <is>
-          <t>ea80743efb1042c9</t>
+          <t>4ea4d7c8874a422f</t>
         </is>
       </c>
       <c r="B209" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.558378Z</t>
+          <t>2026-10-12T05:43:06.782310Z</t>
         </is>
       </c>
       <c r="C209" s="24" t="inlineStr">
         <is>
-          <t>2026-10-07T16:00:00Z</t>
+          <t>2026-10-12T09:00:00Z</t>
         </is>
       </c>
       <c r="D209" s="24" t="inlineStr">
         <is>
-          <t>142771</t>
+          <t>150545</t>
         </is>
       </c>
       <c r="E209" s="24" t="inlineStr">
@@ -67964,12 +68036,12 @@
       </c>
       <c r="F209" s="24" t="inlineStr">
         <is>
-          <t>G2 NORD</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="G209" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics Academy</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="H209" s="24" t="inlineStr">
@@ -67979,7 +68051,7 @@
       </c>
       <c r="I209" s="24" t="inlineStr">
         <is>
-          <t>away</t>
+          <t>home</t>
         </is>
       </c>
       <c r="J209" s="25" t="n"/>
@@ -67989,20 +68061,20 @@
         </is>
       </c>
       <c r="L209" s="26" t="n">
-        <v>-150</v>
+        <v>-213</v>
       </c>
       <c r="M209" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.469484</v>
       </c>
       <c r="N209" s="28" t="n">
-        <v>0.6</v>
+        <v>0.680511</v>
       </c>
       <c r="O209" s="28" t="n">
-        <v>0.507711</v>
+        <v>0.538731</v>
       </c>
       <c r="P209" s="28" t="n"/>
       <c r="Q209" s="28" t="n">
-        <v>-0.092289</v>
+        <v>-0.14178</v>
       </c>
       <c r="R209" s="26" t="n">
         <v>0</v>
@@ -68017,21 +68089,41 @@
       </c>
       <c r="U209" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V209" s="24" t="n"/>
-      <c r="W209" s="26" t="n"/>
-      <c r="X209" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V209" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W209" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X209" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y209" s="25" t="n"/>
-      <c r="Z209" s="26" t="n"/>
-      <c r="AA209" s="28" t="n"/>
-      <c r="AB209" s="28" t="n"/>
-      <c r="AC209" s="30" t="n"/>
-      <c r="AD209" s="24" t="n"/>
+      <c r="Z209" s="26" t="n">
+        <v>-213</v>
+      </c>
+      <c r="AA209" s="28" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AB209" s="28" t="n">
+        <v>-0.000511</v>
+      </c>
+      <c r="AC209" s="30" t="n">
+        <v>0.4695</v>
+      </c>
+      <c r="AD209" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:17:07.668602Z</t>
+        </is>
+      </c>
       <c r="AE209" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.6000 (market_slug=aec-lol-hrts-g2n-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-bfx-jdg-2026-10-12).</t>
         </is>
       </c>
       <c r="AF209" s="31" t="inlineStr">
@@ -68072,32 +68164,32 @@
       </c>
       <c r="AP209" s="24" t="inlineStr">
         <is>
-          <t>G2 NORD</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AQ209" s="24" t="inlineStr">
         <is>
-          <t>G2 NORD</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AR209" s="24" t="inlineStr">
         <is>
-          <t>G2 NORD</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AS209" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics Academy</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AT209" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics Academy</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AU209" s="24" t="inlineStr">
         <is>
-          <t>Team Heretics Academy</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AV209" s="24" t="n"/>
@@ -68115,7 +68207,7 @@
       </c>
       <c r="BA209" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>5137ee43488f994e321771bd9942579f4deaa67d68a7dcd7cccc026e1ec958fd</t>
         </is>
       </c>
       <c r="BB209" s="24" t="inlineStr">
@@ -68130,7 +68222,7 @@
       </c>
       <c r="BD209" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>5137ee43488f994e321771bd9942579f4deaa67d68a7dcd7cccc026e1ec958fd</t>
         </is>
       </c>
       <c r="BE209" s="24" t="inlineStr">
@@ -68150,7 +68242,7 @@
       </c>
       <c r="BH209" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:56.333090Z</t>
+          <t>2026-10-12T05:41:14.138646Z</t>
         </is>
       </c>
       <c r="BI209" s="24" t="inlineStr">
@@ -68160,19 +68252,23 @@
       </c>
       <c r="BJ209" s="25" t="n"/>
       <c r="BK209" s="26" t="n">
-        <v>-150</v>
+        <v>-213</v>
       </c>
       <c r="BL209" s="27" t="n">
-        <v>1.666667</v>
+        <v>1.469484</v>
       </c>
       <c r="BM209" s="28" t="n">
-        <v>0.6</v>
+        <v>0.680511</v>
       </c>
       <c r="BN209" s="28" t="n"/>
       <c r="BO209" s="28" t="n"/>
       <c r="BP209" s="25" t="n"/>
-      <c r="BQ209" s="27" t="n"/>
-      <c r="BR209" s="28" t="n"/>
+      <c r="BQ209" s="27" t="n">
+        <v>1.469484</v>
+      </c>
+      <c r="BR209" s="28" t="n">
+        <v>0.68</v>
+      </c>
       <c r="BS209" s="28" t="n"/>
       <c r="BT209" s="28" t="n"/>
       <c r="BU209" s="25" t="n"/>
@@ -68229,29 +68325,29 @@
       <c r="DP209" s="24" t="n"/>
       <c r="DQ209" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "G2 NORD", "event_id": "142771", "event_start_utc": "2026-10-07T16:00:00Z", "features": {"away_elo": 1916.811779, "away_history_count": 61, "home_elo": 1892.657889, "home_history_count": 157}, "historical_source_observation_times_verified": false, "home_team": "Team Heretics Academy", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16945": 157, "bo3:3:22411": 61}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16945": "2026-09-30T17:30:00Z", "bo3:3:22411": "2026-09-30T16:35:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16945": 1892.657889, "bo3:3:22411": 1916.811779}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16945", "bo3:3:22411"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.507711, "home": 0.492289}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "745fa96b0a908fa8a54d7683111edc4af13ed9b8ca0517c655acbae05e65795c", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "5137ee43488f994e321771bd9942579f4deaa67d68a7dcd7cccc026e1ec958fd", "away_team": "JD Gaming", "event_id": "150545", "event_start_utc": "2026-10-12T09:00:00Z", "features": {"away_elo": 1631.173386, "away_history_count": 172, "home_elo": 1664.536017, "home_history_count": 146}, "historical_source_observation_times_verified": false, "home_team": "BNK FEARX", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18021": 172, "bo3:3:18335": 146}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18021": "2026-10-08T11:00:00Z", "bo3:3:18335": "2026-10-04T07:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06391582132779343, "platt_slope": 0.7835616878097331, "ratings": {"bo3:3:18021": 1631.173386, "bo3:3:18335": 1664.536017}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-12T05:39:31.685941+00:00", "team_ids": ["bo3:3:18335", "bo3:3:18021"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-12T05:39:31.685941+00:00", "probabilities": {"away": 0.461269, "home": 0.538731}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "3e8aa8620e48e7878547b5129c31f374ff4089aaa157ed8cf73eee70622f0908", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
     <row r="210" ht="36" customHeight="1">
       <c r="A210" s="24" t="inlineStr">
         <is>
-          <t>a8edc2ac380f4cf6</t>
+          <t>5178ef11a8fe4c73</t>
         </is>
       </c>
       <c r="B210" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.558378Z</t>
+          <t>2026-10-12T05:43:06.782310Z</t>
         </is>
       </c>
       <c r="C210" s="24" t="inlineStr">
         <is>
-          <t>2026-10-07T21:00:00Z</t>
+          <t>2026-10-12T09:00:00Z</t>
         </is>
       </c>
       <c r="D210" s="24" t="inlineStr">
         <is>
-          <t>144660</t>
+          <t>150545</t>
         </is>
       </c>
       <c r="E210" s="24" t="inlineStr">
@@ -68261,17 +68357,17 @@
       </c>
       <c r="F210" s="24" t="inlineStr">
         <is>
-          <t>Maryville University</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="G210" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="H210" s="24" t="inlineStr">
         <is>
-          <t>moneyline</t>
+          <t>spread</t>
         </is>
       </c>
       <c r="I210" s="24" t="inlineStr">
@@ -68279,27 +68375,29 @@
           <t>away</t>
         </is>
       </c>
-      <c r="J210" s="25" t="n"/>
+      <c r="J210" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="K210" s="24" t="inlineStr">
         <is>
           <t>polymarket_us</t>
         </is>
       </c>
       <c r="L210" s="26" t="n">
-        <v>212</v>
+        <v>-113</v>
       </c>
       <c r="M210" s="27" t="n">
-        <v>3.12</v>
+        <v>1.884956</v>
       </c>
       <c r="N210" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.530516</v>
       </c>
       <c r="O210" s="28" t="n">
-        <v>0.718247</v>
+        <v>0.723488</v>
       </c>
       <c r="P210" s="28" t="n"/>
       <c r="Q210" s="28" t="n">
-        <v>0.397734</v>
+        <v>0.192972</v>
       </c>
       <c r="R210" s="26" t="n">
         <v>100</v>
@@ -68309,26 +68407,40 @@
       </c>
       <c r="T210" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v6</t>
+          <t>lol-spread-tiered-elo-v6</t>
         </is>
       </c>
       <c r="U210" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V210" s="24" t="n"/>
-      <c r="W210" s="26" t="n"/>
-      <c r="X210" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V210" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W210" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X210" s="26" t="n">
+        <v>2</v>
+      </c>
       <c r="Y210" s="25" t="n"/>
       <c r="Z210" s="26" t="n"/>
       <c r="AA210" s="28" t="n"/>
       <c r="AB210" s="28" t="n"/>
-      <c r="AC210" s="30" t="n"/>
-      <c r="AD210" s="24" t="n"/>
+      <c r="AC210" s="30" t="n">
+        <v>1.7699</v>
+      </c>
+      <c r="AD210" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:17:10.597139Z</t>
+        </is>
+      </c>
       <c r="AE210" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.3200 (market_slug=aec-lol-dsg-mvu-2026-10-07).</t>
+          <t>Neutral Elo baseline; executable ask 0.5300 (market_slug=asc-lol-bfx-jdg-2026-10-12-hcap-neg-1pt5).</t>
         </is>
       </c>
       <c r="AF210" s="31" t="inlineStr">
@@ -68369,32 +68481,32 @@
       </c>
       <c r="AP210" s="24" t="inlineStr">
         <is>
-          <t>Maryville University</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AQ210" s="24" t="inlineStr">
         <is>
-          <t>Maryville University</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AR210" s="24" t="inlineStr">
         <is>
-          <t>Maryville University</t>
+          <t>JD Gaming</t>
         </is>
       </c>
       <c r="AS210" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AT210" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AU210" s="24" t="inlineStr">
         <is>
-          <t>Disguised</t>
+          <t>BNK FEARX</t>
         </is>
       </c>
       <c r="AV210" s="24" t="n"/>
@@ -68412,7 +68524,7 @@
       </c>
       <c r="BA210" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>5137ee43488f994e321771bd9942579f4deaa67d68a7dcd7cccc026e1ec958fd</t>
         </is>
       </c>
       <c r="BB210" s="24" t="inlineStr">
@@ -68422,12 +68534,12 @@
       </c>
       <c r="BC210" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v6</t>
+          <t>lol-spread-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BD210" s="24" t="inlineStr">
         <is>
-          <t>e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6</t>
+          <t>5137ee43488f994e321771bd9942579f4deaa67d68a7dcd7cccc026e1ec958fd</t>
         </is>
       </c>
       <c r="BE210" s="24" t="inlineStr">
@@ -68442,12 +68554,12 @@
       </c>
       <c r="BG210" s="24" t="inlineStr">
         <is>
-          <t>lol-tiered-elo-v6</t>
+          <t>lol-spread-tiered-elo-v6</t>
         </is>
       </c>
       <c r="BH210" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:26:06.541945Z</t>
+          <t>2026-10-12T05:41:14.386349Z</t>
         </is>
       </c>
       <c r="BI210" s="24" t="inlineStr">
@@ -68455,15 +68567,17 @@
           <t>["same_event","same_team_same_day","same_league_same_day"]</t>
         </is>
       </c>
-      <c r="BJ210" s="25" t="n"/>
+      <c r="BJ210" s="25" t="n">
+        <v>1.5</v>
+      </c>
       <c r="BK210" s="26" t="n">
-        <v>212</v>
+        <v>-113</v>
       </c>
       <c r="BL210" s="27" t="n">
-        <v>3.12</v>
+        <v>1.884956</v>
       </c>
       <c r="BM210" s="28" t="n">
-        <v>0.320513</v>
+        <v>0.530516</v>
       </c>
       <c r="BN210" s="28" t="n"/>
       <c r="BO210" s="28" t="n"/>
@@ -68524,9 +68638,1566 @@
       <c r="DN210" s="24" t="n"/>
       <c r="DO210" s="24" t="n"/>
       <c r="DP210" s="24" t="n"/>
-      <c r="DQ210" s="24" t="inlineStr">
-        <is>
-          <t>{"artifact_hash": "e669231aab5beee5f198c05063ca9b15af46074b705ecd23d0d44f4ccce4fbb6", "away_team": "Maryville University", "event_id": "144660", "event_start_utc": "2026-10-07T21:00:00Z", "features": {"away_elo": 1646.662988, "away_history_count": 38, "home_elo": 1354.432648, "home_history_count": 67}, "historical_source_observation_times_verified": false, "home_team": "Disguised", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16807": 67, "bo3:3:17077": 38}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16807": "2026-09-06T21:45:00Z", "bo3:3:17077": "2026-10-05T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06641316742326765, "platt_slope": 0.7868066277927818, "ratings": {"bo3:3:16807": 1354.432648, "bo3:3:17077": 1646.662988}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "48eab29fd660f72bcbd6f9557cca081a5e6f76c9da89c9cf36ce7181c79b1174", "features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b"}, "reference_date": "2026-10-06T22:25:25.507143+00:00", "team_ids": ["bo3:3:16807", "bo3:3:17077"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-06T22:25:25.507143+00:00", "probabilities": {"away": 0.718247, "home": 0.281753}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "02872a08071111d998018facd70075414cb67dbd056b333d338af579a3162252", "sport": "LOL"}</t>
+      <c r="DQ210" s="24" t="n"/>
+    </row>
+    <row r="211" ht="36" customHeight="1">
+      <c r="A211" s="24" t="inlineStr">
+        <is>
+          <t>4e27be92166641ee</t>
+        </is>
+      </c>
+      <c r="B211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:29:57.338884Z</t>
+        </is>
+      </c>
+      <c r="C211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T23:00:00Z</t>
+        </is>
+      </c>
+      <c r="D211" s="24" t="inlineStr">
+        <is>
+          <t>153945</t>
+        </is>
+      </c>
+      <c r="E211" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F211" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="G211" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="H211" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I211" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J211" s="25" t="n"/>
+      <c r="K211" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L211" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M211" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N211" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O211" s="28" t="n">
+        <v>0.718608</v>
+      </c>
+      <c r="P211" s="28" t="n"/>
+      <c r="Q211" s="28" t="n">
+        <v>0.308772</v>
+      </c>
+      <c r="R211" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S211" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T211" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U211" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V211" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W211" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X211" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y211" s="25" t="n"/>
+      <c r="Z211" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA211" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB211" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC211" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T04:38:36.245344Z</t>
+        </is>
+      </c>
+      <c r="AE211" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4100 (market_slug=aec-lol-mvu-dsg-2026-10-12).</t>
+        </is>
+      </c>
+      <c r="AF211" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG211" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH211" s="24" t="n"/>
+      <c r="AI211" s="31" t="n"/>
+      <c r="AJ211" s="31" t="n"/>
+      <c r="AK211" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL211" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM211" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN211" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO211" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP211" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AQ211" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AR211" s="24" t="inlineStr">
+        <is>
+          <t>Disguised</t>
+        </is>
+      </c>
+      <c r="AS211" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AT211" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AU211" s="24" t="inlineStr">
+        <is>
+          <t>Maryville University</t>
+        </is>
+      </c>
+      <c r="AV211" s="24" t="n"/>
+      <c r="AW211" s="24" t="n"/>
+      <c r="AX211" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY211" s="24" t="n"/>
+      <c r="AZ211" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA211" s="24" t="inlineStr">
+        <is>
+          <t>6de143ae7e881320a02a25f5cd310612ffb83b18b18b3d0e8b499f5da3c2fcf8</t>
+        </is>
+      </c>
+      <c r="BB211" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC211" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD211" s="24" t="inlineStr">
+        <is>
+          <t>6de143ae7e881320a02a25f5cd310612ffb83b18b18b3d0e8b499f5da3c2fcf8</t>
+        </is>
+      </c>
+      <c r="BE211" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF211" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG211" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH211" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T22:27:24.541326Z</t>
+        </is>
+      </c>
+      <c r="BI211" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ211" s="25" t="n"/>
+      <c r="BK211" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL211" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM211" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN211" s="28" t="n"/>
+      <c r="BO211" s="28" t="n"/>
+      <c r="BP211" s="25" t="n"/>
+      <c r="BQ211" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR211" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BS211" s="28" t="n"/>
+      <c r="BT211" s="28" t="n"/>
+      <c r="BU211" s="25" t="n"/>
+      <c r="BV211" s="29" t="n"/>
+      <c r="BW211" s="24" t="n"/>
+      <c r="BX211" s="30" t="n"/>
+      <c r="BY211" s="27" t="n"/>
+      <c r="BZ211" s="24" t="n"/>
+      <c r="CA211" s="31" t="n"/>
+      <c r="CB211" s="24" t="n"/>
+      <c r="CC211" s="24" t="n"/>
+      <c r="CD211" s="24" t="n"/>
+      <c r="CE211" s="24" t="n"/>
+      <c r="CF211" s="24" t="n"/>
+      <c r="CG211" s="24" t="n"/>
+      <c r="CH211" s="24" t="n"/>
+      <c r="CI211" s="24" t="n"/>
+      <c r="CJ211" s="24" t="n"/>
+      <c r="CK211" s="24" t="n"/>
+      <c r="CL211" s="24" t="n"/>
+      <c r="CM211" s="24" t="n"/>
+      <c r="CN211" s="24" t="n"/>
+      <c r="CO211" s="24" t="n"/>
+      <c r="CP211" s="24" t="n"/>
+      <c r="CQ211" s="24" t="n"/>
+      <c r="CR211" s="24" t="n"/>
+      <c r="CS211" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT211" s="24" t="n"/>
+      <c r="CU211" s="24" t="n"/>
+      <c r="CV211" s="24" t="n"/>
+      <c r="CW211" s="24" t="n"/>
+      <c r="CX211" s="24" t="n"/>
+      <c r="CY211" s="24" t="n"/>
+      <c r="CZ211" s="24" t="n"/>
+      <c r="DA211" s="24" t="n"/>
+      <c r="DB211" s="24" t="n"/>
+      <c r="DC211" s="24" t="n"/>
+      <c r="DD211" s="24" t="n"/>
+      <c r="DE211" s="24" t="n"/>
+      <c r="DF211" s="24" t="n"/>
+      <c r="DG211" s="24" t="n"/>
+      <c r="DH211" s="24" t="n"/>
+      <c r="DI211" s="24" t="n"/>
+      <c r="DJ211" s="24" t="n"/>
+      <c r="DK211" s="24" t="n"/>
+      <c r="DL211" s="24" t="n"/>
+      <c r="DM211" s="24" t="n"/>
+      <c r="DN211" s="24" t="n"/>
+      <c r="DO211" s="24" t="n"/>
+      <c r="DP211" s="24" t="n"/>
+      <c r="DQ211" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "6de143ae7e881320a02a25f5cd310612ffb83b18b18b3d0e8b499f5da3c2fcf8", "away_team": "Disguised", "event_id": "153945", "event_start_utc": "2026-10-12T23:00:00Z", "features": {"away_elo": 1470.024636, "away_history_count": 70, "home_elo": 1708.985153, "home_history_count": 40}, "historical_source_observation_times_verified": false, "home_team": "Maryville University", "inference_inputs": {"book_state": {"games_played": {"bo3:3:16807": 70, "bo3:3:17077": 40}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:16807": "2026-10-10T21:00:00Z", "bo3:3:17077": "2026-10-08T21:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06253227406504594, "platt_slope": 0.7856538446533121, "ratings": {"bo3:3:16807": 1470.024636, "bo3:3:17077": 1708.985153}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-12T22:27:24.244027+00:00", "team_ids": ["bo3:3:17077", "bo3:3:16807"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-12T22:27:24.244027+00:00", "probabilities": {"away": 0.281392, "home": 0.718608}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "b2a92a0ef4e80a3233e00826ed15fec205ac7f62b677edd56c5b3def16bd353c", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="36" customHeight="1">
+      <c r="A212" s="24" t="inlineStr">
+        <is>
+          <t>efc3d223514447f9</t>
+        </is>
+      </c>
+      <c r="B212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:54:20.479309Z</t>
+        </is>
+      </c>
+      <c r="C212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T06:00:00Z</t>
+        </is>
+      </c>
+      <c r="D212" s="24" t="inlineStr">
+        <is>
+          <t>152421</t>
+        </is>
+      </c>
+      <c r="E212" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F212" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="G212" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="H212" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I212" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J212" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K212" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L212" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="M212" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="N212" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="O212" s="28" t="n">
+        <v>0.7229100000000001</v>
+      </c>
+      <c r="P212" s="28" t="n"/>
+      <c r="Q212" s="28" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="R212" s="26" t="n">
+        <v>100</v>
+      </c>
+      <c r="S212" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="T212" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U212" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V212" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W212" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X212" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y212" s="25" t="n"/>
+      <c r="Z212" s="26" t="n"/>
+      <c r="AA212" s="28" t="n"/>
+      <c r="AB212" s="28" t="n"/>
+      <c r="AC212" s="30" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="AD212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T10:09:03.422163Z</t>
+        </is>
+      </c>
+      <c r="AE212" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.3500 (market_slug=asc-lol-we-fly-2026-10-13-hcap-neg-1pt5).</t>
+        </is>
+      </c>
+      <c r="AF212" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG212" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH212" s="24" t="n"/>
+      <c r="AI212" s="31" t="n"/>
+      <c r="AJ212" s="31" t="n"/>
+      <c r="AK212" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL212" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM212" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN212" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO212" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP212" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AQ212" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AR212" s="24" t="inlineStr">
+        <is>
+          <t>FlyQuest</t>
+        </is>
+      </c>
+      <c r="AS212" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AT212" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AU212" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AV212" s="24" t="n"/>
+      <c r="AW212" s="24" t="n"/>
+      <c r="AX212" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY212" s="24" t="n"/>
+      <c r="AZ212" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA212" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BB212" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC212" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD212" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BE212" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF212" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG212" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH212" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:50:53.893217Z</t>
+        </is>
+      </c>
+      <c r="BI212" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ212" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK212" s="26" t="n">
+        <v>186</v>
+      </c>
+      <c r="BL212" s="27" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BM212" s="28" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="BN212" s="28" t="n"/>
+      <c r="BO212" s="28" t="n"/>
+      <c r="BP212" s="25" t="n"/>
+      <c r="BQ212" s="27" t="n"/>
+      <c r="BR212" s="28" t="n"/>
+      <c r="BS212" s="28" t="n"/>
+      <c r="BT212" s="28" t="n"/>
+      <c r="BU212" s="25" t="n"/>
+      <c r="BV212" s="29" t="n"/>
+      <c r="BW212" s="24" t="n"/>
+      <c r="BX212" s="30" t="n"/>
+      <c r="BY212" s="27" t="n"/>
+      <c r="BZ212" s="24" t="n"/>
+      <c r="CA212" s="31" t="n"/>
+      <c r="CB212" s="24" t="n"/>
+      <c r="CC212" s="24" t="n"/>
+      <c r="CD212" s="24" t="n"/>
+      <c r="CE212" s="24" t="n"/>
+      <c r="CF212" s="24" t="n"/>
+      <c r="CG212" s="24" t="n"/>
+      <c r="CH212" s="24" t="n"/>
+      <c r="CI212" s="24" t="n"/>
+      <c r="CJ212" s="24" t="n"/>
+      <c r="CK212" s="24" t="n"/>
+      <c r="CL212" s="24" t="n"/>
+      <c r="CM212" s="24" t="n"/>
+      <c r="CN212" s="24" t="n"/>
+      <c r="CO212" s="24" t="n"/>
+      <c r="CP212" s="24" t="n"/>
+      <c r="CQ212" s="24" t="n"/>
+      <c r="CR212" s="24" t="n"/>
+      <c r="CS212" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT212" s="24" t="n"/>
+      <c r="CU212" s="24" t="n"/>
+      <c r="CV212" s="24" t="n"/>
+      <c r="CW212" s="24" t="n"/>
+      <c r="CX212" s="24" t="n"/>
+      <c r="CY212" s="24" t="n"/>
+      <c r="CZ212" s="24" t="n"/>
+      <c r="DA212" s="24" t="n"/>
+      <c r="DB212" s="24" t="n"/>
+      <c r="DC212" s="24" t="n"/>
+      <c r="DD212" s="24" t="n"/>
+      <c r="DE212" s="24" t="n"/>
+      <c r="DF212" s="24" t="n"/>
+      <c r="DG212" s="24" t="n"/>
+      <c r="DH212" s="24" t="n"/>
+      <c r="DI212" s="24" t="n"/>
+      <c r="DJ212" s="24" t="n"/>
+      <c r="DK212" s="24" t="n"/>
+      <c r="DL212" s="24" t="n"/>
+      <c r="DM212" s="24" t="n"/>
+      <c r="DN212" s="24" t="n"/>
+      <c r="DO212" s="24" t="n"/>
+      <c r="DP212" s="24" t="n"/>
+      <c r="DQ212" s="24" t="n"/>
+    </row>
+    <row r="213" ht="36" customHeight="1">
+      <c r="A213" s="24" t="inlineStr">
+        <is>
+          <t>82c6df908db64dac</t>
+        </is>
+      </c>
+      <c r="B213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:54:20.479309Z</t>
+        </is>
+      </c>
+      <c r="C213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D213" s="24" t="inlineStr">
+        <is>
+          <t>152512</t>
+        </is>
+      </c>
+      <c r="E213" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F213" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G213" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="H213" s="24" t="inlineStr">
+        <is>
+          <t>spread</t>
+        </is>
+      </c>
+      <c r="I213" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J213" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K213" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L213" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="M213" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="N213" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="O213" s="28" t="n">
+        <v>0.687275</v>
+      </c>
+      <c r="P213" s="28" t="n"/>
+      <c r="Q213" s="28" t="n">
+        <v>-0.003127</v>
+      </c>
+      <c r="R213" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S213" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T213" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U213" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V213" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W213" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X213" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y213" s="25" t="n"/>
+      <c r="Z213" s="26" t="n"/>
+      <c r="AA213" s="28" t="n"/>
+      <c r="AB213" s="28" t="n"/>
+      <c r="AC213" s="30" t="n">
+        <v>0.4484</v>
+      </c>
+      <c r="AD213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:44.186243Z</t>
+        </is>
+      </c>
+      <c r="AE213" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6900 (market_slug=asc-lol-bro-lgd-2026-10-13-hcap-pos-1pt5).</t>
+        </is>
+      </c>
+      <c r="AF213" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG213" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH213" s="24" t="n"/>
+      <c r="AI213" s="31" t="n"/>
+      <c r="AJ213" s="31" t="n"/>
+      <c r="AK213" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL213" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM213" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN213" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO213" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP213" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ213" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR213" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS213" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AT213" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AU213" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AV213" s="24" t="n"/>
+      <c r="AW213" s="24" t="n"/>
+      <c r="AX213" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY213" s="24" t="n"/>
+      <c r="AZ213" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA213" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BB213" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC213" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD213" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BE213" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF213" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG213" s="24" t="inlineStr">
+        <is>
+          <t>lol-spread-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH213" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:53:07.034737Z</t>
+        </is>
+      </c>
+      <c r="BI213" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ213" s="25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BK213" s="26" t="n">
+        <v>-223</v>
+      </c>
+      <c r="BL213" s="27" t="n">
+        <v>1.44843</v>
+      </c>
+      <c r="BM213" s="28" t="n">
+        <v>0.690402</v>
+      </c>
+      <c r="BN213" s="28" t="n"/>
+      <c r="BO213" s="28" t="n"/>
+      <c r="BP213" s="25" t="n"/>
+      <c r="BQ213" s="27" t="n"/>
+      <c r="BR213" s="28" t="n"/>
+      <c r="BS213" s="28" t="n"/>
+      <c r="BT213" s="28" t="n"/>
+      <c r="BU213" s="25" t="n"/>
+      <c r="BV213" s="29" t="n"/>
+      <c r="BW213" s="24" t="n"/>
+      <c r="BX213" s="30" t="n"/>
+      <c r="BY213" s="27" t="n"/>
+      <c r="BZ213" s="24" t="n"/>
+      <c r="CA213" s="31" t="n"/>
+      <c r="CB213" s="24" t="n"/>
+      <c r="CC213" s="24" t="n"/>
+      <c r="CD213" s="24" t="n"/>
+      <c r="CE213" s="24" t="n"/>
+      <c r="CF213" s="24" t="n"/>
+      <c r="CG213" s="24" t="n"/>
+      <c r="CH213" s="24" t="n"/>
+      <c r="CI213" s="24" t="n"/>
+      <c r="CJ213" s="24" t="n"/>
+      <c r="CK213" s="24" t="n"/>
+      <c r="CL213" s="24" t="n"/>
+      <c r="CM213" s="24" t="n"/>
+      <c r="CN213" s="24" t="n"/>
+      <c r="CO213" s="24" t="n"/>
+      <c r="CP213" s="24" t="n"/>
+      <c r="CQ213" s="24" t="n"/>
+      <c r="CR213" s="24" t="n"/>
+      <c r="CS213" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT213" s="24" t="n"/>
+      <c r="CU213" s="24" t="n"/>
+      <c r="CV213" s="24" t="n"/>
+      <c r="CW213" s="24" t="n"/>
+      <c r="CX213" s="24" t="n"/>
+      <c r="CY213" s="24" t="n"/>
+      <c r="CZ213" s="24" t="n"/>
+      <c r="DA213" s="24" t="n"/>
+      <c r="DB213" s="24" t="n"/>
+      <c r="DC213" s="24" t="n"/>
+      <c r="DD213" s="24" t="n"/>
+      <c r="DE213" s="24" t="n"/>
+      <c r="DF213" s="24" t="n"/>
+      <c r="DG213" s="24" t="n"/>
+      <c r="DH213" s="24" t="n"/>
+      <c r="DI213" s="24" t="n"/>
+      <c r="DJ213" s="24" t="n"/>
+      <c r="DK213" s="24" t="n"/>
+      <c r="DL213" s="24" t="n"/>
+      <c r="DM213" s="24" t="n"/>
+      <c r="DN213" s="24" t="n"/>
+      <c r="DO213" s="24" t="n"/>
+      <c r="DP213" s="24" t="n"/>
+      <c r="DQ213" s="24" t="n"/>
+    </row>
+    <row r="214" ht="36" customHeight="1">
+      <c r="A214" s="24" t="inlineStr">
+        <is>
+          <t>1fc9bb46814d4066</t>
+        </is>
+      </c>
+      <c r="B214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:54:20.479309Z</t>
+        </is>
+      </c>
+      <c r="C214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D214" s="24" t="inlineStr">
+        <is>
+          <t>152512</t>
+        </is>
+      </c>
+      <c r="E214" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F214" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="G214" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="H214" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I214" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J214" s="25" t="n"/>
+      <c r="K214" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L214" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M214" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N214" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O214" s="28" t="n">
+        <v>0.588411</v>
+      </c>
+      <c r="P214" s="28" t="n"/>
+      <c r="Q214" s="28" t="n">
+        <v>0.04924</v>
+      </c>
+      <c r="R214" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="S214" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T214" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U214" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V214" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W214" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X214" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y214" s="25" t="n"/>
+      <c r="Z214" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="AA214" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB214" s="28" t="n">
+        <v>0.000829</v>
+      </c>
+      <c r="AC214" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T16:17:45.646882Z</t>
+        </is>
+      </c>
+      <c r="AE214" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.5400 (market_slug=aec-lol-bro-lgd-2026-10-13).</t>
+        </is>
+      </c>
+      <c r="AF214" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG214" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH214" s="24" t="n"/>
+      <c r="AI214" s="31" t="n"/>
+      <c r="AJ214" s="31" t="n"/>
+      <c r="AK214" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL214" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM214" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN214" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO214" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP214" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AQ214" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AR214" s="24" t="inlineStr">
+        <is>
+          <t>LGD Gaming</t>
+        </is>
+      </c>
+      <c r="AS214" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AT214" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AU214" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AV214" s="24" t="n"/>
+      <c r="AW214" s="24" t="n"/>
+      <c r="AX214" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY214" s="24" t="n"/>
+      <c r="AZ214" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA214" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BB214" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC214" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD214" s="24" t="inlineStr">
+        <is>
+          <t>4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6</t>
+        </is>
+      </c>
+      <c r="BE214" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF214" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG214" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH214" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T05:53:07.110637Z</t>
+        </is>
+      </c>
+      <c r="BI214" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ214" s="25" t="n"/>
+      <c r="BK214" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL214" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM214" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN214" s="28" t="n"/>
+      <c r="BO214" s="28" t="n"/>
+      <c r="BP214" s="25" t="n"/>
+      <c r="BQ214" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BR214" s="28" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BS214" s="28" t="n"/>
+      <c r="BT214" s="28" t="n"/>
+      <c r="BU214" s="25" t="n"/>
+      <c r="BV214" s="29" t="n"/>
+      <c r="BW214" s="24" t="n"/>
+      <c r="BX214" s="30" t="n"/>
+      <c r="BY214" s="27" t="n"/>
+      <c r="BZ214" s="24" t="n"/>
+      <c r="CA214" s="31" t="n"/>
+      <c r="CB214" s="24" t="n"/>
+      <c r="CC214" s="24" t="n"/>
+      <c r="CD214" s="24" t="n"/>
+      <c r="CE214" s="24" t="n"/>
+      <c r="CF214" s="24" t="n"/>
+      <c r="CG214" s="24" t="n"/>
+      <c r="CH214" s="24" t="n"/>
+      <c r="CI214" s="24" t="n"/>
+      <c r="CJ214" s="24" t="n"/>
+      <c r="CK214" s="24" t="n"/>
+      <c r="CL214" s="24" t="n"/>
+      <c r="CM214" s="24" t="n"/>
+      <c r="CN214" s="24" t="n"/>
+      <c r="CO214" s="24" t="n"/>
+      <c r="CP214" s="24" t="n"/>
+      <c r="CQ214" s="24" t="n"/>
+      <c r="CR214" s="24" t="n"/>
+      <c r="CS214" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT214" s="24" t="n"/>
+      <c r="CU214" s="24" t="n"/>
+      <c r="CV214" s="24" t="n"/>
+      <c r="CW214" s="24" t="n"/>
+      <c r="CX214" s="24" t="n"/>
+      <c r="CY214" s="24" t="n"/>
+      <c r="CZ214" s="24" t="n"/>
+      <c r="DA214" s="24" t="n"/>
+      <c r="DB214" s="24" t="n"/>
+      <c r="DC214" s="24" t="n"/>
+      <c r="DD214" s="24" t="n"/>
+      <c r="DE214" s="24" t="n"/>
+      <c r="DF214" s="24" t="n"/>
+      <c r="DG214" s="24" t="n"/>
+      <c r="DH214" s="24" t="n"/>
+      <c r="DI214" s="24" t="n"/>
+      <c r="DJ214" s="24" t="n"/>
+      <c r="DK214" s="24" t="n"/>
+      <c r="DL214" s="24" t="n"/>
+      <c r="DM214" s="24" t="n"/>
+      <c r="DN214" s="24" t="n"/>
+      <c r="DO214" s="24" t="n"/>
+      <c r="DP214" s="24" t="n"/>
+      <c r="DQ214" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "4df027d27b20080e68bff92c8293fe0ed08143a81bbcd74c2f984d4255029ce6", "away_team": "LGD Gaming", "event_id": "152512", "event_start_utc": "2026-10-13T09:00:00Z", "features": {"away_elo": 1656.696707, "away_history_count": 114, "home_elo": 1542.658013, "home_history_count": 135}, "historical_source_observation_times_verified": false, "home_team": "HANJIN BRION", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17957": 114, "bo3:3:20350": 135}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17957": "2026-10-06T11:15:00Z", "bo3:3:20350": "2026-10-06T07:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06587908043027771, "platt_slope": 0.7892862326027437, "ratings": {"bo3:3:17957": 1656.696707, "bo3:3:20350": 1542.658013}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T05:50:34.289338+00:00", "team_ids": ["bo3:3:20350", "bo3:3:17957"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-13T05:50:34.289338+00:00", "probabilities": {"away": 0.588411, "home": 0.411589}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "811be39846daad73048f62ec5d2243ace3d77682a1f8b69650c820b927c8abe9", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="36" customHeight="1">
+      <c r="A215" s="24" t="inlineStr">
+        <is>
+          <t>baa59c3159b94171</t>
+        </is>
+      </c>
+      <c r="B215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:30:28.211733Z</t>
+        </is>
+      </c>
+      <c r="C215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D215" s="24" t="inlineStr">
+        <is>
+          <t>156611</t>
+        </is>
+      </c>
+      <c r="E215" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F215" s="24" t="inlineStr">
+        <is>
+          <t>BNK FEARX</t>
+        </is>
+      </c>
+      <c r="G215" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster</t>
+        </is>
+      </c>
+      <c r="H215" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I215" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J215" s="25" t="n"/>
+      <c r="K215" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L215" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="M215" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="N215" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="O215" s="28" t="n">
+        <v>0.538121</v>
+      </c>
+      <c r="P215" s="28" t="n"/>
+      <c r="Q215" s="28" t="n">
+        <v>-0.071254</v>
+      </c>
+      <c r="R215" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S215" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T215" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U215" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V215" s="24" t="n"/>
+      <c r="W215" s="26" t="n"/>
+      <c r="X215" s="26" t="n"/>
+      <c r="Y215" s="25" t="n"/>
+      <c r="Z215" s="26" t="n"/>
+      <c r="AA215" s="28" t="n"/>
+      <c r="AB215" s="28" t="n"/>
+      <c r="AC215" s="30" t="n"/>
+      <c r="AD215" s="24" t="n"/>
+      <c r="AE215" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-kt-bfx-2026-10-14).</t>
+        </is>
+      </c>
+      <c r="AF215" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG215" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH215" s="24" t="n"/>
+      <c r="AI215" s="31" t="n"/>
+      <c r="AJ215" s="31" t="n"/>
+      <c r="AK215" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL215" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM215" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN215" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO215" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP215" s="24" t="inlineStr">
+        <is>
+          <t>BNK FEARX</t>
+        </is>
+      </c>
+      <c r="AQ215" s="24" t="inlineStr">
+        <is>
+          <t>BNK FEARX</t>
+        </is>
+      </c>
+      <c r="AR215" s="24" t="inlineStr">
+        <is>
+          <t>BNK FEARX</t>
+        </is>
+      </c>
+      <c r="AS215" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster</t>
+        </is>
+      </c>
+      <c r="AT215" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster</t>
+        </is>
+      </c>
+      <c r="AU215" s="24" t="inlineStr">
+        <is>
+          <t>KT Rolster</t>
+        </is>
+      </c>
+      <c r="AV215" s="24" t="n"/>
+      <c r="AW215" s="24" t="n"/>
+      <c r="AX215" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY215" s="24" t="n"/>
+      <c r="AZ215" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA215" s="24" t="inlineStr">
+        <is>
+          <t>299376ab231303b35e42a3ec79312a649605d948f3ec2ccd1bc24b379189bd2c</t>
+        </is>
+      </c>
+      <c r="BB215" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC215" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD215" s="24" t="inlineStr">
+        <is>
+          <t>299376ab231303b35e42a3ec79312a649605d948f3ec2ccd1bc24b379189bd2c</t>
+        </is>
+      </c>
+      <c r="BE215" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF215" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG215" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:29:28.670613Z</t>
+        </is>
+      </c>
+      <c r="BI215" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ215" s="25" t="n"/>
+      <c r="BK215" s="26" t="n">
+        <v>-156</v>
+      </c>
+      <c r="BL215" s="27" t="n">
+        <v>1.641026</v>
+      </c>
+      <c r="BM215" s="28" t="n">
+        <v>0.609375</v>
+      </c>
+      <c r="BN215" s="28" t="n"/>
+      <c r="BO215" s="28" t="n"/>
+      <c r="BP215" s="25" t="n"/>
+      <c r="BQ215" s="27" t="n"/>
+      <c r="BR215" s="28" t="n"/>
+      <c r="BS215" s="28" t="n"/>
+      <c r="BT215" s="28" t="n"/>
+      <c r="BU215" s="25" t="n"/>
+      <c r="BV215" s="29" t="n"/>
+      <c r="BW215" s="24" t="n"/>
+      <c r="BX215" s="30" t="n"/>
+      <c r="BY215" s="27" t="n"/>
+      <c r="BZ215" s="24" t="n"/>
+      <c r="CA215" s="31" t="n"/>
+      <c r="CB215" s="24" t="n"/>
+      <c r="CC215" s="24" t="n"/>
+      <c r="CD215" s="24" t="n"/>
+      <c r="CE215" s="24" t="n"/>
+      <c r="CF215" s="24" t="n"/>
+      <c r="CG215" s="24" t="n"/>
+      <c r="CH215" s="24" t="n"/>
+      <c r="CI215" s="24" t="n"/>
+      <c r="CJ215" s="24" t="n"/>
+      <c r="CK215" s="24" t="n"/>
+      <c r="CL215" s="24" t="n"/>
+      <c r="CM215" s="24" t="n"/>
+      <c r="CN215" s="24" t="n"/>
+      <c r="CO215" s="24" t="n"/>
+      <c r="CP215" s="24" t="n"/>
+      <c r="CQ215" s="24" t="n"/>
+      <c r="CR215" s="24" t="n"/>
+      <c r="CS215" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT215" s="24" t="n"/>
+      <c r="CU215" s="24" t="n"/>
+      <c r="CV215" s="24" t="n"/>
+      <c r="CW215" s="24" t="n"/>
+      <c r="CX215" s="24" t="n"/>
+      <c r="CY215" s="24" t="n"/>
+      <c r="CZ215" s="24" t="n"/>
+      <c r="DA215" s="24" t="n"/>
+      <c r="DB215" s="24" t="n"/>
+      <c r="DC215" s="24" t="n"/>
+      <c r="DD215" s="24" t="n"/>
+      <c r="DE215" s="24" t="n"/>
+      <c r="DF215" s="24" t="n"/>
+      <c r="DG215" s="24" t="n"/>
+      <c r="DH215" s="24" t="n"/>
+      <c r="DI215" s="24" t="n"/>
+      <c r="DJ215" s="24" t="n"/>
+      <c r="DK215" s="24" t="n"/>
+      <c r="DL215" s="24" t="n"/>
+      <c r="DM215" s="24" t="n"/>
+      <c r="DN215" s="24" t="n"/>
+      <c r="DO215" s="24" t="n"/>
+      <c r="DP215" s="24" t="n"/>
+      <c r="DQ215" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "299376ab231303b35e42a3ec79312a649605d948f3ec2ccd1bc24b379189bd2c", "away_team": "BNK FEARX", "event_id": "156611", "event_start_utc": "2026-10-14T09:00:00Z", "features": {"away_elo": 1696.549683, "away_history_count": 147, "home_elo": 1722.551961, "home_history_count": 151}, "historical_source_observation_times_verified": false, "home_team": "KT Rolster", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18156": 151, "bo3:3:18335": 147}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18156": "2026-10-12T06:00:00Z", "bo3:3:18335": "2026-10-12T10:30:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06590547113706442, "platt_slope": 0.7862898525737445, "ratings": {"bo3:3:18156": 1722.551961, "bo3:3:18335": 1696.549683}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "8d25951d04320147b4f82f35408c7948ac3d6a80af203ada3bac1aa630e7b330", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-13T22:29:06.680882+00:00", "team_ids": ["bo3:3:18156", "bo3:3:18335"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-13T22:29:06.680882+00:00", "probabilities": {"away": 0.461879, "home": 0.538121}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "a5b678ed10ba67f87efc0617dea5a7e2a490c19438fca4f232d3b7502a2df687", "sport": "LOL"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/lol/gated.xlsx
+++ b/data/sports/lol/gated.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ215" headerRowCount="1">
-  <autoFilter ref="A1:DQ215"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ217" headerRowCount="1">
+  <autoFilter ref="A1:DQ217"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$215)</f>
+        <f>COUNTA('Picks'!$A$2:$A$217)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$215,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$217,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")+COUNTIFS('Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$215,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$217,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")/(COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"win")+COUNTIFS('Picks'!$BX$2:$BX$215,"&gt;0",'Picks'!$V$2:$V$215,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")/(COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"win")+COUNTIFS('Picks'!$BX$2:$BX$217,"&gt;0",'Picks'!$V$2:$V$217,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$215)/SUM('Picks'!$BX$2:$BX$215),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$217)/SUM('Picks'!$BX$2:$BX$217),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$215)</f>
+        <f>SUM('Picks'!$BY$2:$BY$217)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$215,"&lt;&gt;",'Picks'!$AB$2:$AB$215),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$217,"&lt;&gt;",'Picks'!$AB$2:$AB$217),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$217,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$215,'Picks'!$AM$2:$AM$215,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$217,'Picks'!$AM$2:$AM$217,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A14,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A14,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A15,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A15,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled",'Picks'!$V$2:$V$215,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled",'Picks'!$V$2:$V$217,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$215,'Picks'!$H$2:$H$215,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$217,'Picks'!$H$2:$H$217,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$215,'Picks'!$H$2:$H$215,$A16,'Picks'!$U$2:$U$215,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$217,'Picks'!$H$2:$H$217,$A16,'Picks'!$U$2:$U$217,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ215"/>
+  <dimension ref="A1:DQ217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -70201,6 +70201,600 @@
         </is>
       </c>
     </row>
+    <row r="216" ht="36" customHeight="1">
+      <c r="A216" s="24" t="inlineStr">
+        <is>
+          <t>79f1c581e04b422b</t>
+        </is>
+      </c>
+      <c r="B216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:54:07.491288Z</t>
+        </is>
+      </c>
+      <c r="C216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T09:00:00Z</t>
+        </is>
+      </c>
+      <c r="D216" s="24" t="inlineStr">
+        <is>
+          <t>158355</t>
+        </is>
+      </c>
+      <c r="E216" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F216" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="G216" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="H216" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I216" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J216" s="25" t="n"/>
+      <c r="K216" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L216" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="M216" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="N216" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="O216" s="28" t="n">
+        <v>0.585194</v>
+      </c>
+      <c r="P216" s="28" t="n"/>
+      <c r="Q216" s="28" t="n">
+        <v>0.104425</v>
+      </c>
+      <c r="R216" s="26" t="n">
+        <v>72</v>
+      </c>
+      <c r="S216" s="29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T216" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U216" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V216" s="24" t="n"/>
+      <c r="W216" s="26" t="n"/>
+      <c r="X216" s="26" t="n"/>
+      <c r="Y216" s="25" t="n"/>
+      <c r="Z216" s="26" t="n"/>
+      <c r="AA216" s="28" t="n"/>
+      <c r="AB216" s="28" t="n"/>
+      <c r="AC216" s="30" t="n"/>
+      <c r="AD216" s="24" t="n"/>
+      <c r="AE216" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-we-bro-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF216" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG216" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH216" s="24" t="n"/>
+      <c r="AI216" s="31" t="n"/>
+      <c r="AJ216" s="31" t="n"/>
+      <c r="AK216" s="24" t="inlineStr">
+        <is>
+          <t>model_qualified</t>
+        </is>
+      </c>
+      <c r="AL216" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM216" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED_SHADOW_CALL</t>
+        </is>
+      </c>
+      <c r="AN216" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO216" s="24" t="inlineStr">
+        <is>
+          <t>QUALIFIED</t>
+        </is>
+      </c>
+      <c r="AP216" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AQ216" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AR216" s="24" t="inlineStr">
+        <is>
+          <t>HANJIN BRION</t>
+        </is>
+      </c>
+      <c r="AS216" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AT216" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AU216" s="24" t="inlineStr">
+        <is>
+          <t>Team WE</t>
+        </is>
+      </c>
+      <c r="AV216" s="24" t="n"/>
+      <c r="AW216" s="24" t="n"/>
+      <c r="AX216" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY216" s="24" t="n"/>
+      <c r="AZ216" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA216" s="24" t="inlineStr">
+        <is>
+          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+        </is>
+      </c>
+      <c r="BB216" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC216" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD216" s="24" t="inlineStr">
+        <is>
+          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+        </is>
+      </c>
+      <c r="BE216" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF216" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG216" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH216" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:53:56.897143Z</t>
+        </is>
+      </c>
+      <c r="BI216" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ216" s="25" t="n"/>
+      <c r="BK216" s="26" t="n">
+        <v>108</v>
+      </c>
+      <c r="BL216" s="27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="BM216" s="28" t="n">
+        <v>0.480769</v>
+      </c>
+      <c r="BN216" s="28" t="n"/>
+      <c r="BO216" s="28" t="n"/>
+      <c r="BP216" s="25" t="n"/>
+      <c r="BQ216" s="27" t="n"/>
+      <c r="BR216" s="28" t="n"/>
+      <c r="BS216" s="28" t="n"/>
+      <c r="BT216" s="28" t="n"/>
+      <c r="BU216" s="25" t="n"/>
+      <c r="BV216" s="29" t="n"/>
+      <c r="BW216" s="24" t="n"/>
+      <c r="BX216" s="30" t="n"/>
+      <c r="BY216" s="27" t="n"/>
+      <c r="BZ216" s="24" t="n"/>
+      <c r="CA216" s="31" t="n"/>
+      <c r="CB216" s="24" t="n"/>
+      <c r="CC216" s="24" t="n"/>
+      <c r="CD216" s="24" t="n"/>
+      <c r="CE216" s="24" t="n"/>
+      <c r="CF216" s="24" t="n"/>
+      <c r="CG216" s="24" t="n"/>
+      <c r="CH216" s="24" t="n"/>
+      <c r="CI216" s="24" t="n"/>
+      <c r="CJ216" s="24" t="n"/>
+      <c r="CK216" s="24" t="n"/>
+      <c r="CL216" s="24" t="n"/>
+      <c r="CM216" s="24" t="n"/>
+      <c r="CN216" s="24" t="n"/>
+      <c r="CO216" s="24" t="n"/>
+      <c r="CP216" s="24" t="n"/>
+      <c r="CQ216" s="24" t="n"/>
+      <c r="CR216" s="24" t="n"/>
+      <c r="CS216" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT216" s="24" t="n"/>
+      <c r="CU216" s="24" t="n"/>
+      <c r="CV216" s="24" t="n"/>
+      <c r="CW216" s="24" t="n"/>
+      <c r="CX216" s="24" t="n"/>
+      <c r="CY216" s="24" t="n"/>
+      <c r="CZ216" s="24" t="n"/>
+      <c r="DA216" s="24" t="n"/>
+      <c r="DB216" s="24" t="n"/>
+      <c r="DC216" s="24" t="n"/>
+      <c r="DD216" s="24" t="n"/>
+      <c r="DE216" s="24" t="n"/>
+      <c r="DF216" s="24" t="n"/>
+      <c r="DG216" s="24" t="n"/>
+      <c r="DH216" s="24" t="n"/>
+      <c r="DI216" s="24" t="n"/>
+      <c r="DJ216" s="24" t="n"/>
+      <c r="DK216" s="24" t="n"/>
+      <c r="DL216" s="24" t="n"/>
+      <c r="DM216" s="24" t="n"/>
+      <c r="DN216" s="24" t="n"/>
+      <c r="DO216" s="24" t="n"/>
+      <c r="DP216" s="24" t="n"/>
+      <c r="DQ216" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5", "away_team": "HANJIN BRION", "event_id": "158355", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1589.742977, "away_history_count": 136, "home_elo": 1665.755954, "home_history_count": 148}, "historical_source_observation_times_verified": false, "home_team": "Team WE", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17801": 148, "bo3:3:20350": 136}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17801": "2026-10-13T06:00:00Z", "bo3:3:20350": "2026-10-13T10:50:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06590547113706442, "platt_slope": 0.7862898525737445, "ratings": {"bo3:3:17801": 1665.755954, "bo3:3:20350": 1589.742977}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:13.841820+00:00", "team_ids": ["bo3:3:17801", "bo3:3:20350"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:13.841820+00:00", "probabilities": {"away": 0.414806, "home": 0.585194}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "90a1f8ad307e7a1656a02ef5cc7a15c206fe2806a9adda3a739d8d70dfa80cc6", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="36" customHeight="1">
+      <c r="A217" s="24" t="inlineStr">
+        <is>
+          <t>bcbfceed4b444c79</t>
+        </is>
+      </c>
+      <c r="B217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:54:07.491288Z</t>
+        </is>
+      </c>
+      <c r="C217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-15T18:00:00Z</t>
+        </is>
+      </c>
+      <c r="D217" s="24" t="inlineStr">
+        <is>
+          <t>159574</t>
+        </is>
+      </c>
+      <c r="E217" s="24" t="inlineStr">
+        <is>
+          <t>LOL</t>
+        </is>
+      </c>
+      <c r="F217" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 Kia</t>
+        </is>
+      </c>
+      <c r="G217" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp</t>
+        </is>
+      </c>
+      <c r="H217" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I217" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J217" s="25" t="n"/>
+      <c r="K217" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L217" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="M217" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="N217" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="O217" s="28" t="n">
+        <v>0.631588</v>
+      </c>
+      <c r="P217" s="28" t="n"/>
+      <c r="Q217" s="28" t="n">
+        <v>-0.06811200000000001</v>
+      </c>
+      <c r="R217" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S217" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T217" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="U217" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V217" s="24" t="n"/>
+      <c r="W217" s="26" t="n"/>
+      <c r="X217" s="26" t="n"/>
+      <c r="Y217" s="25" t="n"/>
+      <c r="Z217" s="26" t="n"/>
+      <c r="AA217" s="28" t="n"/>
+      <c r="AB217" s="28" t="n"/>
+      <c r="AC217" s="30" t="n"/>
+      <c r="AD217" s="24" t="n"/>
+      <c r="AE217" s="31" t="inlineStr">
+        <is>
+          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-kc-c9-2026-10-15).</t>
+        </is>
+      </c>
+      <c r="AF217" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted esports baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG217" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH217" s="24" t="n"/>
+      <c r="AI217" s="31" t="n"/>
+      <c r="AJ217" s="31" t="n"/>
+      <c r="AK217" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL217" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM217" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN217" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO217" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_MODEL_UNVALIDATED</t>
+        </is>
+      </c>
+      <c r="AP217" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 Kia</t>
+        </is>
+      </c>
+      <c r="AQ217" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 Kia</t>
+        </is>
+      </c>
+      <c r="AR217" s="24" t="inlineStr">
+        <is>
+          <t>Cloud9 Kia</t>
+        </is>
+      </c>
+      <c r="AS217" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp</t>
+        </is>
+      </c>
+      <c r="AT217" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp</t>
+        </is>
+      </c>
+      <c r="AU217" s="24" t="inlineStr">
+        <is>
+          <t>Karmine Corp</t>
+        </is>
+      </c>
+      <c r="AV217" s="24" t="n"/>
+      <c r="AW217" s="24" t="n"/>
+      <c r="AX217" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY217" s="24" t="n"/>
+      <c r="AZ217" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA217" s="24" t="inlineStr">
+        <is>
+          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+        </is>
+      </c>
+      <c r="BB217" s="24" t="inlineStr">
+        <is>
+          <t>neutral_elo</t>
+        </is>
+      </c>
+      <c r="BC217" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BD217" s="24" t="inlineStr">
+        <is>
+          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+        </is>
+      </c>
+      <c r="BE217" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF217" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG217" s="24" t="inlineStr">
+        <is>
+          <t>lol-tiered-elo-v6</t>
+        </is>
+      </c>
+      <c r="BH217" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T05:54:07.232606Z</t>
+        </is>
+      </c>
+      <c r="BI217" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ217" s="25" t="n"/>
+      <c r="BK217" s="26" t="n">
+        <v>-233</v>
+      </c>
+      <c r="BL217" s="27" t="n">
+        <v>1.429185</v>
+      </c>
+      <c r="BM217" s="28" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="BN217" s="28" t="n"/>
+      <c r="BO217" s="28" t="n"/>
+      <c r="BP217" s="25" t="n"/>
+      <c r="BQ217" s="27" t="n"/>
+      <c r="BR217" s="28" t="n"/>
+      <c r="BS217" s="28" t="n"/>
+      <c r="BT217" s="28" t="n"/>
+      <c r="BU217" s="25" t="n"/>
+      <c r="BV217" s="29" t="n"/>
+      <c r="BW217" s="24" t="n"/>
+      <c r="BX217" s="30" t="n"/>
+      <c r="BY217" s="27" t="n"/>
+      <c r="BZ217" s="24" t="n"/>
+      <c r="CA217" s="31" t="n"/>
+      <c r="CB217" s="24" t="n"/>
+      <c r="CC217" s="24" t="n"/>
+      <c r="CD217" s="24" t="n"/>
+      <c r="CE217" s="24" t="n"/>
+      <c r="CF217" s="24" t="n"/>
+      <c r="CG217" s="24" t="n"/>
+      <c r="CH217" s="24" t="n"/>
+      <c r="CI217" s="24" t="n"/>
+      <c r="CJ217" s="24" t="n"/>
+      <c r="CK217" s="24" t="n"/>
+      <c r="CL217" s="24" t="n"/>
+      <c r="CM217" s="24" t="n"/>
+      <c r="CN217" s="24" t="n"/>
+      <c r="CO217" s="24" t="n"/>
+      <c r="CP217" s="24" t="n"/>
+      <c r="CQ217" s="24" t="n"/>
+      <c r="CR217" s="24" t="n"/>
+      <c r="CS217" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT217" s="24" t="n"/>
+      <c r="CU217" s="24" t="n"/>
+      <c r="CV217" s="24" t="n"/>
+      <c r="CW217" s="24" t="n"/>
+      <c r="CX217" s="24" t="n"/>
+      <c r="CY217" s="24" t="n"/>
+      <c r="CZ217" s="24" t="n"/>
+      <c r="DA217" s="24" t="n"/>
+      <c r="DB217" s="24" t="n"/>
+      <c r="DC217" s="24" t="n"/>
+      <c r="DD217" s="24" t="n"/>
+      <c r="DE217" s="24" t="n"/>
+      <c r="DF217" s="24" t="n"/>
+      <c r="DG217" s="24" t="n"/>
+      <c r="DH217" s="24" t="n"/>
+      <c r="DI217" s="24" t="n"/>
+      <c r="DJ217" s="24" t="n"/>
+      <c r="DK217" s="24" t="n"/>
+      <c r="DL217" s="24" t="n"/>
+      <c r="DM217" s="24" t="n"/>
+      <c r="DN217" s="24" t="n"/>
+      <c r="DO217" s="24" t="n"/>
+      <c r="DP217" s="24" t="n"/>
+      <c r="DQ217" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5", "away_team": "Cloud9 Kia", "event_id": "159574", "event_start_utc": "2026-10-15T18:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1858.367725, "home_history_count": 131}, "historical_source_observation_times_verified": false, "home_team": "Karmine Corp", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18342": 131}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18342": "2026-09-19T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06590547113706442, "platt_slope": 0.7862898525737445, "ratings": {"bo3:3:18342": 1858.367725}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:13.841820+00:00", "team_ids": ["bo3:3:18342", "unknown:cloud9kia"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:13.841820+00:00", "probabilities": {"away": 0.368412, "home": 0.631588}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "efe6192a357ef99bd7b4d91b3e3a19c958d842c66a908ef4a6a3761fc6f3ba82", "sport": "LOL"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/lol/gated.xlsx
+++ b/data/sports/lol/gated.xlsx
@@ -69985,18 +69985,38 @@
       </c>
       <c r="U215" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V215" s="24" t="n"/>
-      <c r="W215" s="26" t="n"/>
-      <c r="X215" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V215" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W215" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X215" s="26" t="n">
+        <v>0</v>
+      </c>
       <c r="Y215" s="25" t="n"/>
-      <c r="Z215" s="26" t="n"/>
-      <c r="AA215" s="28" t="n"/>
-      <c r="AB215" s="28" t="n"/>
-      <c r="AC215" s="30" t="n"/>
-      <c r="AD215" s="24" t="n"/>
+      <c r="Z215" s="26" t="n">
+        <v>-150</v>
+      </c>
+      <c r="AA215" s="28" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AB215" s="28" t="n">
+        <v>-0.009375</v>
+      </c>
+      <c r="AC215" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD215" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T16:17:56.109066Z</t>
+        </is>
+      </c>
       <c r="AE215" s="31" t="inlineStr">
         <is>
           <t>Neutral Elo baseline; executable ask 0.6100 (market_slug=aec-lol-kt-bfx-2026-10-14).</t>
@@ -70009,7 +70029,7 @@
       </c>
       <c r="AG215" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH215" s="24" t="n"/>
@@ -70139,8 +70159,12 @@
       <c r="BN215" s="28" t="n"/>
       <c r="BO215" s="28" t="n"/>
       <c r="BP215" s="25" t="n"/>
-      <c r="BQ215" s="27" t="n"/>
-      <c r="BR215" s="28" t="n"/>
+      <c r="BQ215" s="27" t="n">
+        <v>1.666667</v>
+      </c>
+      <c r="BR215" s="28" t="n">
+        <v>0.6</v>
+      </c>
       <c r="BS215" s="28" t="n"/>
       <c r="BT215" s="28" t="n"/>
       <c r="BU215" s="25" t="n"/>
@@ -70204,12 +70228,12 @@
     <row r="216" ht="36" customHeight="1">
       <c r="A216" s="24" t="inlineStr">
         <is>
-          <t>79f1c581e04b422b</t>
+          <t>7dfe3d1443764352</t>
         </is>
       </c>
       <c r="B216" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:54:07.491288Z</t>
+          <t>2026-10-14T22:46:32.899589Z</t>
         </is>
       </c>
       <c r="C216" s="24" t="inlineStr">
@@ -70254,26 +70278,26 @@
         </is>
       </c>
       <c r="L216" s="26" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="M216" s="27" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="N216" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.45045</v>
       </c>
       <c r="O216" s="28" t="n">
-        <v>0.585194</v>
+        <v>0.584651</v>
       </c>
       <c r="P216" s="28" t="n"/>
       <c r="Q216" s="28" t="n">
-        <v>0.104425</v>
+        <v>0.134201</v>
       </c>
       <c r="R216" s="26" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="S216" s="29" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="T216" s="24" t="inlineStr">
         <is>
@@ -70296,7 +70320,7 @@
       <c r="AD216" s="24" t="n"/>
       <c r="AE216" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.4800 (market_slug=aec-lol-we-bro-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.4500 (market_slug=aec-lol-we-bro-2026-10-15).</t>
         </is>
       </c>
       <c r="AF216" s="31" t="inlineStr">
@@ -70380,7 +70404,7 @@
       </c>
       <c r="BA216" s="24" t="inlineStr">
         <is>
-          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+          <t>d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa</t>
         </is>
       </c>
       <c r="BB216" s="24" t="inlineStr">
@@ -70395,7 +70419,7 @@
       </c>
       <c r="BD216" s="24" t="inlineStr">
         <is>
-          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+          <t>d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa</t>
         </is>
       </c>
       <c r="BE216" s="24" t="inlineStr">
@@ -70415,7 +70439,7 @@
       </c>
       <c r="BH216" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:53:56.897143Z</t>
+          <t>2026-10-14T22:46:32.752057Z</t>
         </is>
       </c>
       <c r="BI216" s="24" t="inlineStr">
@@ -70425,13 +70449,13 @@
       </c>
       <c r="BJ216" s="25" t="n"/>
       <c r="BK216" s="26" t="n">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="BL216" s="27" t="n">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="BM216" s="28" t="n">
-        <v>0.480769</v>
+        <v>0.45045</v>
       </c>
       <c r="BN216" s="28" t="n"/>
       <c r="BO216" s="28" t="n"/>
@@ -70494,19 +70518,19 @@
       <c r="DP216" s="24" t="n"/>
       <c r="DQ216" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5", "away_team": "HANJIN BRION", "event_id": "158355", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1589.742977, "away_history_count": 136, "home_elo": 1665.755954, "home_history_count": 148}, "historical_source_observation_times_verified": false, "home_team": "Team WE", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17801": 148, "bo3:3:20350": 136}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17801": "2026-10-13T06:00:00Z", "bo3:3:20350": "2026-10-13T10:50:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06590547113706442, "platt_slope": 0.7862898525737445, "ratings": {"bo3:3:17801": 1665.755954, "bo3:3:20350": 1589.742977}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:13.841820+00:00", "team_ids": ["bo3:3:17801", "bo3:3:20350"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:13.841820+00:00", "probabilities": {"away": 0.414806, "home": 0.585194}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "90a1f8ad307e7a1656a02ef5cc7a15c206fe2806a9adda3a739d8d70dfa80cc6", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa", "away_team": "HANJIN BRION", "event_id": "158355", "event_start_utc": "2026-10-15T09:00:00Z", "features": {"away_elo": 1589.493329, "away_history_count": 136, "home_elo": 1665.58905, "home_history_count": 148}, "historical_source_observation_times_verified": false, "home_team": "Team WE", "inference_inputs": {"book_state": {"games_played": {"bo3:3:17801": 148, "bo3:3:20350": 136}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:17801": "2026-10-13T06:00:00Z", "bo3:3:20350": "2026-10-13T10:50:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0647425941447472, "platt_slope": 0.7870787842362164, "ratings": {"bo3:3:17801": 1665.58905, "bo3:3:20350": 1589.493329}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.677057+00:00", "team_ids": ["bo3:3:17801", "bo3:3:20350"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.677057+00:00", "probabilities": {"away": 0.415349, "home": 0.584651}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "bc8f73fa8802b5da5f390dcd0e87be32693e30934291460a8946ef8e92841eb9", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
     <row r="217" ht="36" customHeight="1">
       <c r="A217" s="24" t="inlineStr">
         <is>
-          <t>bcbfceed4b444c79</t>
+          <t>d8ff862bbb924f3e</t>
         </is>
       </c>
       <c r="B217" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:54:07.491288Z</t>
+          <t>2026-10-14T22:46:32.899589Z</t>
         </is>
       </c>
       <c r="C217" s="24" t="inlineStr">
@@ -70551,20 +70575,20 @@
         </is>
       </c>
       <c r="L217" s="26" t="n">
-        <v>-233</v>
+        <v>-213</v>
       </c>
       <c r="M217" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.469484</v>
       </c>
       <c r="N217" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.680511</v>
       </c>
       <c r="O217" s="28" t="n">
-        <v>0.631588</v>
+        <v>0.631049</v>
       </c>
       <c r="P217" s="28" t="n"/>
       <c r="Q217" s="28" t="n">
-        <v>-0.06811200000000001</v>
+        <v>-0.049462</v>
       </c>
       <c r="R217" s="26" t="n">
         <v>0</v>
@@ -70593,7 +70617,7 @@
       <c r="AD217" s="24" t="n"/>
       <c r="AE217" s="31" t="inlineStr">
         <is>
-          <t>Neutral Elo baseline; executable ask 0.7000 (market_slug=aec-lol-kc-c9-2026-10-15).</t>
+          <t>Neutral Elo baseline; executable ask 0.6800 (market_slug=aec-lol-kc-c9-2026-10-15).</t>
         </is>
       </c>
       <c r="AF217" s="31" t="inlineStr">
@@ -70677,7 +70701,7 @@
       </c>
       <c r="BA217" s="24" t="inlineStr">
         <is>
-          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+          <t>d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa</t>
         </is>
       </c>
       <c r="BB217" s="24" t="inlineStr">
@@ -70692,7 +70716,7 @@
       </c>
       <c r="BD217" s="24" t="inlineStr">
         <is>
-          <t>f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5</t>
+          <t>d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa</t>
         </is>
       </c>
       <c r="BE217" s="24" t="inlineStr">
@@ -70712,7 +70736,7 @@
       </c>
       <c r="BH217" s="24" t="inlineStr">
         <is>
-          <t>2026-10-14T05:54:07.232606Z</t>
+          <t>2026-10-14T22:46:32.818011Z</t>
         </is>
       </c>
       <c r="BI217" s="24" t="inlineStr">
@@ -70722,13 +70746,13 @@
       </c>
       <c r="BJ217" s="25" t="n"/>
       <c r="BK217" s="26" t="n">
-        <v>-233</v>
+        <v>-213</v>
       </c>
       <c r="BL217" s="27" t="n">
-        <v>1.429185</v>
+        <v>1.469484</v>
       </c>
       <c r="BM217" s="28" t="n">
-        <v>0.6997</v>
+        <v>0.680511</v>
       </c>
       <c r="BN217" s="28" t="n"/>
       <c r="BO217" s="28" t="n"/>
@@ -70791,7 +70815,7 @@
       <c r="DP217" s="24" t="n"/>
       <c r="DQ217" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "f5aef11083f55ed36d6cabad7160d2d277b4f4496bf6dea5b43d73c6591ae2a5", "away_team": "Cloud9 Kia", "event_id": "159574", "event_start_utc": "2026-10-15T18:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1858.367725, "home_history_count": 131}, "historical_source_observation_times_verified": false, "home_team": "Karmine Corp", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18342": 131}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18342": "2026-09-19T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.06590547113706442, "platt_slope": 0.7862898525737445, "ratings": {"bo3:3:18342": 1858.367725}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T05:52:13.841820+00:00", "team_ids": ["bo3:3:18342", "unknown:cloud9kia"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T05:52:13.841820+00:00", "probabilities": {"away": 0.368412, "home": 0.631588}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "efe6192a357ef99bd7b4d91b3e3a19c958d842c66a908ef4a6a3761fc6f3ba82", "sport": "LOL"}</t>
+          <t>{"artifact_hash": "d358fca331260cfa69faaef983d0e2d69de8e3668821f8965c16218890d9f3aa", "away_team": "Cloud9 Kia", "event_id": "159574", "event_start_utc": "2026-10-15T18:00:00Z", "features": {"away_elo": 1500.0, "away_history_count": 0, "home_elo": 1858.37132, "home_history_count": 131}, "historical_source_observation_times_verified": false, "home_team": "Karmine Corp", "inference_inputs": {"book_state": {"games_played": {"bo3:3:18342": 131}, "inactivity_half_life_days": null, "inactivity_max_pull": null, "k": 48.0, "last_match_utc": {"bo3:3:18342": "2026-09-19T15:00:00Z"}, "minimum_reliable_games": null, "platt_intercept": 0.0647425941447472, "platt_slope": 0.7870787842362164, "ratings": {"bo3:3:18342": 1858.37132}, "recency_half_life_days": null, "recency_max_boost": null, "temperature": 1.18, "thin_data_max_shrink": null, "tier_weights": null}, "code_sha256": {"esports.py": "3abbfc5d7124cc94603dada2e4c996da231a679d437c5a066d994a2a7d428f61", "features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872"}, "reference_date": "2026-10-14T22:46:32.677057+00:00", "team_ids": ["bo3:3:18342", "unknown:cloud9kia"]}, "market_type": "moneyline", "model_version": "lol-tiered-elo-v6", "observed_at_utc": "2026-10-14T22:46:32.677057+00:00", "probabilities": {"away": 0.368951, "home": 0.631049}, "replay_scope": "Exact serving book state, calibration, temperature, inactivity reference and thin-history adjustments; training provenance not certified.", "schema": "esports-elo-replay-v1", "snapshot_hash": "e9c4544fbf6d7e72a933c8aea4a5e58f550ace00c0287c9d17205163361c8e03", "sport": "LOL"}</t>
         </is>
       </c>
     </row>
